--- a/docs/projects/mihomes/MHO_model.xlsx
+++ b/docs/projects/mihomes/MHO_model.xlsx
@@ -26,7 +26,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;(#,##0.00);&quot;—&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;—&quot;"/>
@@ -37,7 +37,6 @@
     <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="172" formatCode="#,##0.00;(#,##0.00);&quot;—&quot;00"/>
     <numFmt numFmtId="173" formatCode="$#,##0"/>
-    <numFmt numFmtId="174" formatCode="#,##0.00;(#,##0.00);&quot;—&quot;0"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -143,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,6 +179,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -266,7 +269,6 @@
     <xf numFmtId="168" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1112,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:Q40"/>
+  <dimension ref="B2:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.2" customWidth="1" min="1" max="1"/>
@@ -1150,127 +1152,127 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="68" t="inlineStr">
+      <c r="B5" s="70" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="C5" s="69" t="inlineStr">
+      <c r="C5" s="71" t="inlineStr">
         <is>
           <t>Price $</t>
         </is>
       </c>
-      <c r="D5" s="69" t="inlineStr">
+      <c r="D5" s="71" t="inlineStr">
         <is>
           <t>Mkt cap $m</t>
         </is>
       </c>
-      <c r="E5" s="69" t="inlineStr">
+      <c r="E5" s="71" t="inlineStr">
         <is>
           <t>Equity $m</t>
         </is>
       </c>
-      <c r="F5" s="69" t="inlineStr">
+      <c r="F5" s="71" t="inlineStr">
         <is>
           <t>GW+int $m</t>
         </is>
       </c>
-      <c r="G5" s="69" t="inlineStr">
+      <c r="G5" s="71" t="inlineStr">
         <is>
           <t>P/E ttm</t>
         </is>
       </c>
-      <c r="H5" s="69" t="inlineStr">
+      <c r="H5" s="71" t="inlineStr">
         <is>
           <t>Rev ttm $m</t>
         </is>
       </c>
-      <c r="I5" s="69" t="inlineStr">
+      <c r="I5" s="71" t="inlineStr">
         <is>
           <t>NI ttm $m</t>
         </is>
       </c>
-      <c r="J5" s="69" t="inlineStr">
+      <c r="J5" s="71" t="inlineStr">
         <is>
           <t>Shares m</t>
         </is>
       </c>
-      <c r="K5" s="69" t="inlineStr">
+      <c r="K5" s="71" t="inlineStr">
         <is>
           <t>BVPS $</t>
         </is>
       </c>
-      <c r="L5" s="69" t="inlineStr">
+      <c r="L5" s="71" t="inlineStr">
         <is>
           <t>TBVPS $</t>
         </is>
       </c>
-      <c r="M5" s="69" t="inlineStr">
+      <c r="M5" s="71" t="inlineStr">
         <is>
           <t>P/B</t>
         </is>
       </c>
-      <c r="N5" s="69" t="inlineStr">
+      <c r="N5" s="71" t="inlineStr">
         <is>
           <t>P/TB</t>
         </is>
       </c>
-      <c r="O5" s="69" t="inlineStr">
+      <c r="O5" s="71" t="inlineStr">
         <is>
           <t>ROE %</t>
         </is>
       </c>
-      <c r="P5" s="69" t="inlineStr">
+      <c r="P5" s="71" t="inlineStr">
         <is>
           <t>P/E x ROE</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="70" t="inlineStr">
+      <c r="B6" s="72" t="inlineStr">
         <is>
           <t>DHI — D.R. Horton</t>
         </is>
       </c>
-      <c r="C6" s="38" t="n">
+      <c r="C6" s="40" t="n">
         <v>142.94</v>
       </c>
-      <c r="D6" s="39" t="n">
+      <c r="D6" s="41" t="n">
         <v>39980</v>
       </c>
-      <c r="E6" s="39" t="n">
+      <c r="E6" s="41" t="n">
         <v>23820</v>
       </c>
-      <c r="F6" s="39" t="n">
+      <c r="F6" s="41" t="n">
         <v>164</v>
       </c>
-      <c r="G6" s="71" t="n">
+      <c r="G6" s="73" t="n">
         <v>13.6</v>
       </c>
-      <c r="H6" s="39" t="n">
+      <c r="H6" s="41" t="n">
         <v>33350</v>
       </c>
       <c r="I6" s="13">
         <f>D6/G6</f>
         <v/>
       </c>
-      <c r="J6" s="46">
+      <c r="J6" s="48">
         <f>D6/C6</f>
         <v/>
       </c>
-      <c r="K6" s="48">
+      <c r="K6" s="50">
         <f>E6/J6</f>
         <v/>
       </c>
-      <c r="L6" s="48">
+      <c r="L6" s="50">
         <f>(E6-F6)/J6</f>
         <v/>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="60">
         <f>C6/K6</f>
         <v/>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="60">
         <f>C6/L6</f>
         <v/>
       </c>
@@ -1278,56 +1280,56 @@
         <f>I6/E6</f>
         <v/>
       </c>
-      <c r="P6" s="72">
+      <c r="P6" s="74">
         <f>G6*O6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="70" t="inlineStr">
+      <c r="B7" s="72" t="inlineStr">
         <is>
           <t>LEN — Lennar</t>
         </is>
       </c>
-      <c r="C7" s="38" t="n">
+      <c r="C7" s="40" t="n">
         <v>83.88</v>
       </c>
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="41" t="n">
         <v>20210</v>
       </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="41" t="n">
         <v>21621</v>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F7" s="41" t="n">
         <v>3632</v>
       </c>
-      <c r="G7" s="71" t="n">
+      <c r="G7" s="73" t="n">
         <v>13.12</v>
       </c>
-      <c r="H7" s="39" t="n">
+      <c r="H7" s="41" t="n">
         <v>32740</v>
       </c>
       <c r="I7" s="13">
         <f>D7/G7</f>
         <v/>
       </c>
-      <c r="J7" s="46">
+      <c r="J7" s="48">
         <f>D7/C7</f>
         <v/>
       </c>
-      <c r="K7" s="48">
+      <c r="K7" s="50">
         <f>E7/J7</f>
         <v/>
       </c>
-      <c r="L7" s="48">
+      <c r="L7" s="50">
         <f>(E7-F7)/J7</f>
         <v/>
       </c>
-      <c r="M7" s="58">
+      <c r="M7" s="60">
         <f>C7/K7</f>
         <v/>
       </c>
-      <c r="N7" s="58">
+      <c r="N7" s="60">
         <f>C7/L7</f>
         <v/>
       </c>
@@ -1335,56 +1337,56 @@
         <f>I7/E7</f>
         <v/>
       </c>
-      <c r="P7" s="72">
+      <c r="P7" s="74">
         <f>G7*O7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="70" t="inlineStr">
+      <c r="B8" s="72" t="inlineStr">
         <is>
           <t>PHM — PulteGroup</t>
         </is>
       </c>
-      <c r="C8" s="38" t="n">
+      <c r="C8" s="40" t="n">
         <v>124.36</v>
       </c>
-      <c r="D8" s="39" t="n">
+      <c r="D8" s="41" t="n">
         <v>23310</v>
       </c>
-      <c r="E8" s="39" t="n">
+      <c r="E8" s="41" t="n">
         <v>13014</v>
       </c>
-      <c r="F8" s="39" t="n">
+      <c r="F8" s="41" t="n">
         <v>86</v>
       </c>
-      <c r="G8" s="71" t="n">
+      <c r="G8" s="73" t="n">
         <v>12.68</v>
       </c>
-      <c r="H8" s="39" t="n">
+      <c r="H8" s="41" t="n">
         <v>16410</v>
       </c>
       <c r="I8" s="13">
         <f>D8/G8</f>
         <v/>
       </c>
-      <c r="J8" s="46">
+      <c r="J8" s="48">
         <f>D8/C8</f>
         <v/>
       </c>
-      <c r="K8" s="48">
+      <c r="K8" s="50">
         <f>E8/J8</f>
         <v/>
       </c>
-      <c r="L8" s="48">
+      <c r="L8" s="50">
         <f>(E8-F8)/J8</f>
         <v/>
       </c>
-      <c r="M8" s="58">
+      <c r="M8" s="60">
         <f>C8/K8</f>
         <v/>
       </c>
-      <c r="N8" s="58">
+      <c r="N8" s="60">
         <f>C8/L8</f>
         <v/>
       </c>
@@ -1392,56 +1394,56 @@
         <f>I8/E8</f>
         <v/>
       </c>
-      <c r="P8" s="72">
+      <c r="P8" s="74">
         <f>G8*O8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="70" t="inlineStr">
+      <c r="B9" s="72" t="inlineStr">
         <is>
           <t>TOL — Toll Brothers</t>
         </is>
       </c>
-      <c r="C9" s="38" t="n">
+      <c r="C9" s="40" t="n">
         <v>141.43</v>
       </c>
-      <c r="D9" s="39" t="n">
+      <c r="D9" s="41" t="n">
         <v>13030</v>
       </c>
-      <c r="E9" s="39" t="n">
+      <c r="E9" s="41" t="n">
         <v>8531</v>
       </c>
-      <c r="F9" s="39" t="n">
+      <c r="F9" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="71" t="n">
+      <c r="G9" s="73" t="n">
         <v>11.32</v>
       </c>
-      <c r="H9" s="39" t="n">
+      <c r="H9" s="41" t="n">
         <v>10760</v>
       </c>
       <c r="I9" s="13">
         <f>D9/G9</f>
         <v/>
       </c>
-      <c r="J9" s="46">
+      <c r="J9" s="48">
         <f>D9/C9</f>
         <v/>
       </c>
-      <c r="K9" s="48">
+      <c r="K9" s="50">
         <f>E9/J9</f>
         <v/>
       </c>
-      <c r="L9" s="48">
+      <c r="L9" s="50">
         <f>(E9-F9)/J9</f>
         <v/>
       </c>
-      <c r="M9" s="58">
+      <c r="M9" s="60">
         <f>C9/K9</f>
         <v/>
       </c>
-      <c r="N9" s="58">
+      <c r="N9" s="60">
         <f>C9/L9</f>
         <v/>
       </c>
@@ -1449,56 +1451,56 @@
         <f>I9/E9</f>
         <v/>
       </c>
-      <c r="P9" s="72">
+      <c r="P9" s="74">
         <f>G9*O9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="70" t="inlineStr">
-        <is>
-          <t>MTH — Meritage Homes</t>
-        </is>
-      </c>
-      <c r="C10" s="38" t="n">
+      <c r="B10" s="72" t="inlineStr">
+        <is>
+          <t>MTH — Meritage</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="n">
         <v>67.75</v>
       </c>
-      <c r="D10" s="39" t="n">
+      <c r="D10" s="41" t="n">
         <v>4420</v>
       </c>
-      <c r="E10" s="39" t="n">
+      <c r="E10" s="41" t="n">
         <v>5058</v>
       </c>
-      <c r="F10" s="39" t="n">
+      <c r="F10" s="41" t="n">
         <v>34</v>
       </c>
-      <c r="G10" s="71" t="n">
+      <c r="G10" s="73" t="n">
         <v>14.07</v>
       </c>
-      <c r="H10" s="39" t="n">
+      <c r="H10" s="41" t="n">
         <v>5390</v>
       </c>
       <c r="I10" s="13">
         <f>D10/G10</f>
         <v/>
       </c>
-      <c r="J10" s="46">
+      <c r="J10" s="48">
         <f>D10/C10</f>
         <v/>
       </c>
-      <c r="K10" s="48">
+      <c r="K10" s="50">
         <f>E10/J10</f>
         <v/>
       </c>
-      <c r="L10" s="48">
+      <c r="L10" s="50">
         <f>(E10-F10)/J10</f>
         <v/>
       </c>
-      <c r="M10" s="58">
+      <c r="M10" s="60">
         <f>C10/K10</f>
         <v/>
       </c>
-      <c r="N10" s="58">
+      <c r="N10" s="60">
         <f>C10/L10</f>
         <v/>
       </c>
@@ -1506,56 +1508,56 @@
         <f>I10/E10</f>
         <v/>
       </c>
-      <c r="P10" s="72">
+      <c r="P10" s="74">
         <f>G10*O10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="70" t="inlineStr">
-        <is>
-          <t>TPH — Tri Pointe Homes</t>
-        </is>
-      </c>
-      <c r="C11" s="38" t="n">
+      <c r="B11" s="72" t="inlineStr">
+        <is>
+          <t>TPH — Tri Pointe</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="n">
         <v>46.95</v>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D11" s="41" t="n">
         <v>4000</v>
       </c>
-      <c r="E11" s="39" t="n">
+      <c r="E11" s="41" t="n">
         <v>3141</v>
       </c>
-      <c r="F11" s="39" t="n">
+      <c r="F11" s="41" t="n">
         <v>156</v>
       </c>
-      <c r="G11" s="71" t="n">
+      <c r="G11" s="73" t="n">
         <v>22.24</v>
       </c>
-      <c r="H11" s="39" t="n">
+      <c r="H11" s="41" t="n">
         <v>3250</v>
       </c>
       <c r="I11" s="13">
         <f>D11/G11</f>
         <v/>
       </c>
-      <c r="J11" s="46">
+      <c r="J11" s="48">
         <f>D11/C11</f>
         <v/>
       </c>
-      <c r="K11" s="48">
+      <c r="K11" s="50">
         <f>E11/J11</f>
         <v/>
       </c>
-      <c r="L11" s="48">
+      <c r="L11" s="50">
         <f>(E11-F11)/J11</f>
         <v/>
       </c>
-      <c r="M11" s="58">
+      <c r="M11" s="60">
         <f>C11/K11</f>
         <v/>
       </c>
-      <c r="N11" s="58">
+      <c r="N11" s="60">
         <f>C11/L11</f>
         <v/>
       </c>
@@ -1563,7 +1565,7 @@
         <f>I11/E11</f>
         <v/>
       </c>
-      <c r="P11" s="72">
+      <c r="P11" s="74">
         <f>G11*O11</f>
         <v/>
       </c>
@@ -1578,7 +1580,7 @@
       <c r="D12" s="19" t="n"/>
       <c r="E12" s="19" t="n"/>
       <c r="F12" s="19" t="n"/>
-      <c r="G12" s="73">
+      <c r="G12" s="75">
         <f>MEDIAN(G6:G11)</f>
         <v/>
       </c>
@@ -1587,88 +1589,88 @@
       <c r="J12" s="19" t="n"/>
       <c r="K12" s="19" t="n"/>
       <c r="L12" s="19" t="n"/>
-      <c r="M12" s="73">
+      <c r="M12" s="75">
         <f>MEDIAN(M6:M11)</f>
         <v/>
       </c>
-      <c r="N12" s="73">
+      <c r="N12" s="75">
         <f>MEDIAN(N6:N11)</f>
         <v/>
       </c>
-      <c r="O12" s="74">
+      <c r="O12" s="76">
         <f>MEDIAN(O6:O11)</f>
         <v/>
       </c>
       <c r="P12" s="19" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>Peer mean</t>
         </is>
       </c>
-      <c r="G13" s="75">
+      <c r="G13" s="77">
         <f>AVERAGE(G6:G11)</f>
         <v/>
       </c>
-      <c r="M13" s="75">
+      <c r="M13" s="77">
         <f>AVERAGE(M6:M11)</f>
         <v/>
       </c>
-      <c r="N13" s="75">
+      <c r="N13" s="77">
         <f>AVERAGE(N6:N11)</f>
         <v/>
       </c>
-      <c r="O13" s="32">
+      <c r="O13" s="34">
         <f>AVERAGE(O6:O11)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>MHO — M/I Homes</t>
         </is>
       </c>
-      <c r="C14" s="76" t="n">
+      <c r="C14" s="78" t="n">
         <v>148.26</v>
       </c>
-      <c r="D14" s="77" t="n">
+      <c r="D14" s="79" t="n">
         <v>3748</v>
       </c>
-      <c r="E14" s="77" t="n">
+      <c r="E14" s="79" t="n">
         <v>3227</v>
       </c>
-      <c r="F14" s="77" t="n">
+      <c r="F14" s="79" t="n">
         <v>16</v>
       </c>
-      <c r="G14" s="78" t="n">
+      <c r="G14" s="80" t="n">
         <v>12.41</v>
       </c>
-      <c r="H14" s="77" t="n">
+      <c r="H14" s="79" t="n">
         <v>4260</v>
       </c>
-      <c r="I14" s="62">
+      <c r="I14" s="64">
         <f>D14/G14</f>
         <v/>
       </c>
-      <c r="J14" s="79">
+      <c r="J14" s="81">
         <f>D14/C14</f>
         <v/>
       </c>
-      <c r="K14" s="80">
+      <c r="K14" s="82">
         <f>E14/J14</f>
         <v/>
       </c>
-      <c r="L14" s="80">
+      <c r="L14" s="82">
         <f>(E14-F14)/J14</f>
         <v/>
       </c>
-      <c r="M14" s="81">
+      <c r="M14" s="83">
         <f>C14/K14</f>
         <v/>
       </c>
-      <c r="N14" s="81">
+      <c r="N14" s="83">
         <f>C14/L14</f>
         <v/>
       </c>
@@ -1676,7 +1678,7 @@
         <f>I14/E14</f>
         <v/>
       </c>
-      <c r="P14" s="81">
+      <c r="P14" s="83">
         <f>G14*O14</f>
         <v/>
       </c>
@@ -1689,7 +1691,7 @@
     <row r="16" ht="15.5" customHeight="1">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>WHY THE MEDIAN MULTIPLE IS THE WRONG ANCHOR</t>
+          <t>WHAT THE COMP SET ACTUALLY SHOWS</t>
         </is>
       </c>
       <c r="C16" s="3" t="n"/>
@@ -1710,35 +1712,35 @@
     <row r="17">
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>P/B = (MktCap/NI) x (NI/Equity) = P/E x ROE. That is an accounting identity, not an empirical result — the P/E x ROE column below reproduces P/B exactly for every company.</t>
+          <t>P/B = (MktCap/NI) x (NI/Equity) = P/E x ROE. That is an accounting identity, not an empirical result — the P/E x ROE column above reproduces P/B exactly for every company.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>So the high R-squared on the regression is largely mechanical. What the regression really measures is how TIGHTLY peer P/Es cluster: ex-Tri Pointe they span 11.3x to 14.1x, a</t>
+          <t>So there is no independent information in a fitted line through P/B and ROE, and none is attempted here. The observation that survives is about DISPERSION: peer earnings</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>coefficient of variation of 7%, while ROE ranges 6.2% to 14.1%, a CoV of 31%. Because the P/E term is nearly constant, the book multiple is close to a restatement of the return.</t>
+          <t>multiples sit in a narrow band while returns on equity do not. The market is paying similar earnings multiples for very different returns on capital.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>That is still the useful conclusion — a builder's book multiple is set by its return on book — but it is worth an order of magnitude less than a 0.94 R-squared implies, and it means</t>
+          <t>The practical consequence: P/B and P/E are ONE view of this stock, not two, so they are counted once. And because the multiple barely moves with the return, MHO's</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>the P/B and P/E comparables are ONE view, not two. Note also that dropping Tri Pointe (22x P/E, trough earnings) moves R-squared from 0.77 to 0.94 on a sample of five.</t>
+          <t>depressed ROE shows up in the earnings rather than in the multiple — which is why the peer-based valuation below simply applies the peer median P/E to our own EPS estimate.</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1748,7 @@
     <row r="23" ht="15.5" customHeight="1">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>REGRESSION — peer P/B on trailing ROE (excluding TPH)</t>
+          <t>DISPERSION — peer earnings multiples vs peer returns (Tri Pointe shown but excluded: its 22x P/E reflects trough earnings)</t>
         </is>
       </c>
       <c r="C23" s="3" t="n"/>
@@ -1767,298 +1769,212 @@
     <row r="24">
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Slope — P/B per 1.00 of ROE</t>
-        </is>
-      </c>
-      <c r="E24" s="48">
-        <f>SLOPE(M6:M10,O6:O10)</f>
+          <t>Peer P/E — low</t>
+        </is>
+      </c>
+      <c r="E24" s="60">
+        <f>MIN(G6:G10)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   i.e. per percentage point of ROE</t>
-        </is>
-      </c>
-      <c r="E25" s="61">
-        <f>E24/100</f>
-        <v/>
-      </c>
-      <c r="Q25" s="9" t="inlineStr">
-        <is>
-          <t>Roughly 0.11x of book for every point of return on equity.</t>
-        </is>
+          <t>Peer P/E — high</t>
+        </is>
+      </c>
+      <c r="E25" s="60">
+        <f>MAX(G6:G10)</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="E26" s="82">
-        <f>INTERCEPT(M6:M10,O6:O10)</f>
-        <v/>
+          <t>Peer P/E — coefficient of variation</t>
+        </is>
+      </c>
+      <c r="E26" s="16">
+        <f>STDEVP(G6:G10)/AVERAGE(G6:G10)</f>
+        <v/>
+      </c>
+      <c r="Q26" s="9" t="inlineStr">
+        <is>
+          <t>Earnings multiples are tightly clustered.</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="E27" s="48">
-        <f>RSQ(M6:M10,O6:O10)</f>
-        <v/>
-      </c>
-      <c r="Q27" s="9" t="inlineStr">
-        <is>
-          <t>Book multiple is almost entirely explained by return on book.</t>
-        </is>
+          <t>Peer ROE — low</t>
+        </is>
+      </c>
+      <c r="E27" s="16">
+        <f>MIN(O6:O10)</f>
+        <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Implied fair P/B at MHO trailing ROE</t>
-        </is>
-      </c>
-      <c r="E28" s="81">
-        <f>$E$26+$E$24*O14</f>
-        <v/>
-      </c>
-      <c r="Q28" s="9" t="inlineStr">
-        <is>
-          <t>Compare with MHO's actual P/B in the table above. The stock already carries some recovery in the price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="6" customHeight="1"/>
-    <row r="30" ht="15.5" customHeight="1">
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Peer ROE — high</t>
+        </is>
+      </c>
+      <c r="E28" s="16">
+        <f>MAX(O6:O10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Peer ROE — coefficient of variation</t>
+        </is>
+      </c>
+      <c r="E29" s="12">
+        <f>STDEVP(O6:O10)/AVERAGE(O6:O10)</f>
+        <v/>
+      </c>
+      <c r="Q29" s="9" t="inlineStr">
+        <is>
+          <t>Returns vary roughly four times as much as the multiples that price them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31">
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Normalised ROE implied by the current share price</t>
+        </is>
+      </c>
+      <c r="E31" s="84">
+        <f>3.5+M14*(DCF!$C$9-3.5)</f>
+        <v/>
+      </c>
+      <c r="Q31" s="9" t="inlineStr">
+        <is>
+          <t>At an 11.5% cost of equity and 3.5% long-run growth, a 1.16x book multiple already pays for a normalised return on equity of roughly 12.8%. The base case reaches 12.2% by 2029, so the recovery is largely in the price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="6" customHeight="1"/>
+    <row r="33" ht="15.5" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>IMPLIED VALUE PER SHARE</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3" t="n"/>
-      <c r="O30" s="3" t="n"/>
-      <c r="P30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="15" t="inlineStr">
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3" t="n"/>
+      <c r="O33" s="3" t="n"/>
+      <c r="P33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>Applied to</t>
         </is>
       </c>
-      <c r="H31" s="15" t="inlineStr">
+      <c r="H34" s="15" t="inlineStr">
         <is>
           <t>Value $</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Normalised ROE implied by the current share price</t>
-        </is>
-      </c>
-      <c r="E32" s="83">
-        <f>3.5+M14*(DCF!$C$9-3.5)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="9" t="inlineStr">
-        <is>
-          <t>Invert the residual income model: at a 11.5% cost of equity and 3.5% growth, a 1.16x book multiple is already paying for a normalised return on equity of roughly 12.8%. Our base case reaches 12.2% by 2029. The recovery is in the price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="6" customHeight="1"/>
-    <row r="34" ht="15.5" customHeight="1">
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>IMPLIED VALUE PER SHARE</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3" t="n"/>
-      <c r="O34" s="3" t="n"/>
-      <c r="P34" s="3" t="n"/>
-    </row>
     <row r="35">
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>Multiple</t>
-        </is>
-      </c>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
-          <t>Applied to</t>
-        </is>
-      </c>
-      <c r="H35" s="15" t="inlineStr">
-        <is>
-          <t>Value $</t>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Peer median P/B on Sep-2027E book</t>
+        </is>
+      </c>
+      <c r="C35" s="60">
+        <f>M12</f>
+        <v/>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Book value at Sep-2027 (est.)</t>
+        </is>
+      </c>
+      <c r="H35" s="85">
+        <f>C35*((BS!F25)+(BS!G25))/2</f>
+        <v/>
+      </c>
+      <c r="Q35" s="9" t="inlineStr">
+        <is>
+          <t>THE comparables method. The median multiple the comp set trades at, applied to our own book estimate. Scenarios instead take the multiple the market puts on the builder actually earning that return — Meritage for the bear case, Toll Brothers for the bull — so every multiple in the model belongs to a company you can look up.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Peer median P/B — unadjusted</t>
-        </is>
-      </c>
-      <c r="C36" s="58">
-        <f>M12</f>
+          <t>Memo: peer median P/E on 2027E EPS</t>
+        </is>
+      </c>
+      <c r="C36" s="60">
+        <f>G12</f>
         <v/>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Book value at Sep-2027 (est.)</t>
-        </is>
-      </c>
-      <c r="H36" s="84">
-        <f>C36*((BS!F25)+(BS!G25))/2</f>
+          <t>2027E diluted EPS</t>
+        </is>
+      </c>
+      <c r="H36" s="85">
+        <f>C36*IS!G37</f>
         <v/>
       </c>
       <c r="Q36" s="9" t="inlineStr">
         <is>
-          <t>The naive answer: assumes MHO deserves the average builder multiple regardless of the return it earns.</t>
+          <t>Cross-check only, NOT weighted. The identity P/B = P/E x ROE means this is the same view restated.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Regression P/B at 2027E ROE</t>
-        </is>
-      </c>
-      <c r="C37" s="58">
-        <f>$E$26+$E$24*BS!G29</f>
+          <t>Memo: MHO's own P/E on 2027E EPS</t>
+        </is>
+      </c>
+      <c r="C37" s="60">
+        <f>G14</f>
         <v/>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Book value at Sep-2027 (est.)</t>
-        </is>
-      </c>
-      <c r="H37" s="84">
-        <f>C37*((BS!F25)+(BS!G25))/2</f>
+          <t>2027E diluted EPS</t>
+        </is>
+      </c>
+      <c r="H37" s="85">
+        <f>C37*IS!G37</f>
         <v/>
       </c>
       <c r="Q37" s="9" t="inlineStr">
         <is>
-          <t>Return-adjusted. The regression is fitted on peers' TRAILING returns, so it is applied to the ROE that will be trailing at the target date — 2027E, not 2028E. Using a further-forward ROE would double-count the recovery the peers already embed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>Justified P/B = (ROE − g)/(COE − g)</t>
-        </is>
-      </c>
-      <c r="C38" s="58">
-        <f>(BS!I29*100-3.5)/(DCF!$C$9-3.5)</f>
-        <v/>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Book value at Sep-2027 (est.)</t>
-        </is>
-      </c>
-      <c r="H38" s="84">
-        <f>C38*((BS!F25)+(BS!G25))/2</f>
-        <v/>
-      </c>
-      <c r="Q38" s="9" t="inlineStr">
-        <is>
-          <t>Residual income, using normalised 2029E ROE, 3.5% growth and the CAPM cost of equity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>Peer median P/E on 2027E EPS</t>
-        </is>
-      </c>
-      <c r="C39" s="58">
-        <f>G12</f>
-        <v/>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>2027E diluted EPS</t>
-        </is>
-      </c>
-      <c r="H39" s="84">
-        <f>C39*IS!G37</f>
-        <v/>
-      </c>
-      <c r="Q39" s="9" t="inlineStr">
-        <is>
-          <t>Earnings multiples are a weak anchor for builders — the E is cyclical and the multiple compresses at the peak.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>11.0x 2027E EPS (return-adjusted)</t>
-        </is>
-      </c>
-      <c r="C40" s="71" t="n">
-        <v>11</v>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>2027E diluted EPS</t>
-        </is>
-      </c>
-      <c r="H40" s="84">
-        <f>C40*IS!G37</f>
-        <v/>
-      </c>
-      <c r="Q40" s="9" t="inlineStr">
-        <is>
-          <t>A discount to the peer P/E, consistent with the ROE gap.</t>
+          <t>NOT a valuation. This reduces algebraically to today's share price scaled by our own EPS growth, so it cannot disagree with the market. Shown only to document why it is not used.</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2042,7 @@
           <t>Deliveries — Northern</t>
         </is>
       </c>
-      <c r="C6" s="49">
+      <c r="C6" s="51">
         <f>'Segment Build'!G8</f>
         <v/>
       </c>
@@ -2137,7 +2053,7 @@
           <t>Deliveries — Southern</t>
         </is>
       </c>
-      <c r="C7" s="49">
+      <c r="C7" s="51">
         <f>'Segment Build'!G18</f>
         <v/>
       </c>
@@ -2148,7 +2064,7 @@
           <t>Gross ASP — Northern ($000)</t>
         </is>
       </c>
-      <c r="C8" s="53">
+      <c r="C8" s="55">
         <f>'Segment Build'!G9</f>
         <v/>
       </c>
@@ -2159,7 +2075,7 @@
           <t>Gross ASP — Southern ($000)</t>
         </is>
       </c>
-      <c r="C9" s="53">
+      <c r="C9" s="55">
         <f>'Segment Build'!G19</f>
         <v/>
       </c>
@@ -2170,7 +2086,7 @@
           <t>Cost per home — Northern ($000)</t>
         </is>
       </c>
-      <c r="C10" s="53">
+      <c r="C10" s="55">
         <f>'Segment Build'!G12</f>
         <v/>
       </c>
@@ -2181,7 +2097,7 @@
           <t>Cost per home — Southern ($000)</t>
         </is>
       </c>
-      <c r="C11" s="53">
+      <c r="C11" s="55">
         <f>'Segment Build'!G22</f>
         <v/>
       </c>
@@ -2192,7 +2108,7 @@
           <t>Land sale revenue</t>
         </is>
       </c>
-      <c r="C12" s="49">
+      <c r="C12" s="51">
         <f>Assumptions!G28</f>
         <v/>
       </c>
@@ -2203,7 +2119,7 @@
           <t>Financial services revenue</t>
         </is>
       </c>
-      <c r="C13" s="49">
+      <c r="C13" s="51">
         <f>'Segment Build'!G29</f>
         <v/>
       </c>
@@ -2214,7 +2130,7 @@
           <t>Diluted shares (000)</t>
         </is>
       </c>
-      <c r="C14" s="49">
+      <c r="C14" s="51">
         <f>IS!G36</f>
         <v/>
       </c>
@@ -2225,7 +2141,7 @@
           <t>Northern competition premium (pp)</t>
         </is>
       </c>
-      <c r="C15" s="85">
+      <c r="C15" s="86">
         <f>Assumptions!G14</f>
         <v/>
       </c>
@@ -2236,7 +2152,7 @@
           <t>Neutral mortgage rate (%)</t>
         </is>
       </c>
-      <c r="C16" s="85">
+      <c r="C16" s="86">
         <f>Assumptions!$C$9</f>
         <v/>
       </c>
@@ -2247,7 +2163,7 @@
           <t>Northern base incentive / rate slope</t>
         </is>
       </c>
-      <c r="C17" s="85">
+      <c r="C17" s="86">
         <f>Assumptions!$C$12</f>
         <v/>
       </c>
@@ -2258,7 +2174,7 @@
           <t xml:space="preserve">   Northern rate slope</t>
         </is>
       </c>
-      <c r="C18" s="86">
+      <c r="C18" s="87">
         <f>Assumptions!$C$13</f>
         <v/>
       </c>
@@ -2269,7 +2185,7 @@
           <t>Southern base incentive</t>
         </is>
       </c>
-      <c r="C19" s="85">
+      <c r="C19" s="86">
         <f>Assumptions!$C$15</f>
         <v/>
       </c>
@@ -2280,7 +2196,7 @@
           <t xml:space="preserve">   Southern rate slope</t>
         </is>
       </c>
-      <c r="C20" s="86">
+      <c r="C20" s="87">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
@@ -2291,7 +2207,7 @@
           <t>Selling (% of homebuilding revenue)</t>
         </is>
       </c>
-      <c r="C21" s="85">
+      <c r="C21" s="86">
         <f>Assumptions!G30</f>
         <v/>
       </c>
@@ -2302,7 +2218,7 @@
           <t>Homebuilding G&amp;A (% of homebuilding revenue)</t>
         </is>
       </c>
-      <c r="C22" s="85">
+      <c r="C22" s="86">
         <f>Assumptions!G31</f>
         <v/>
       </c>
@@ -2313,7 +2229,7 @@
           <t>Financial services pre-tax margin (%)</t>
         </is>
       </c>
-      <c r="C23" s="85">
+      <c r="C23" s="86">
         <f>Assumptions!$C$37</f>
         <v/>
       </c>
@@ -2324,7 +2240,7 @@
           <t>Corporate / unallocated</t>
         </is>
       </c>
-      <c r="C24" s="49">
+      <c r="C24" s="51">
         <f>Assumptions!G32</f>
         <v/>
       </c>
@@ -2335,7 +2251,7 @@
           <t>Inventory impairment</t>
         </is>
       </c>
-      <c r="C25" s="49">
+      <c r="C25" s="51">
         <f>Assumptions!G33</f>
         <v/>
       </c>
@@ -2346,7 +2262,7 @@
           <t>Net interest income</t>
         </is>
       </c>
-      <c r="C26" s="49">
+      <c r="C26" s="51">
         <f>Assumptions!G34</f>
         <v/>
       </c>
@@ -2357,7 +2273,7 @@
           <t>Tax rate (%)</t>
         </is>
       </c>
-      <c r="C27" s="85">
+      <c r="C27" s="86">
         <f>Assumptions!$C$38</f>
         <v/>
       </c>
@@ -2368,7 +2284,7 @@
           <t>Land gross margin (%)</t>
         </is>
       </c>
-      <c r="C28" s="85">
+      <c r="C28" s="86">
         <f>Assumptions!$C$35</f>
         <v/>
       </c>
@@ -2379,7 +2295,7 @@
           <t>Southern share of land revenue (%)</t>
         </is>
       </c>
-      <c r="C29" s="87">
+      <c r="C29" s="88">
         <f>Assumptions!$C$36</f>
         <v/>
       </c>
@@ -2401,29 +2317,29 @@
       <c r="J31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B32" s="32" t="inlineStr">
         <is>
           <t>30-yr mortgage rate  \  competition premium (pp of gross ASP)</t>
         </is>
       </c>
-      <c r="C32" s="65" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" s="65" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E32" s="65" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F32" s="65" t="n">
-        <v>6</v>
-      </c>
-      <c r="G32" s="65" t="n">
-        <v>7.5</v>
+      <c r="C32" s="67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D32" s="67" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E32" s="67" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F32" s="67" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G32" s="67" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="65" t="n">
+      <c r="B33" s="67" t="n">
         <v>5.5</v>
       </c>
       <c r="C33" s="11">
@@ -2453,7 +2369,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="65" t="n">
+      <c r="B34" s="67" t="n">
         <v>6</v>
       </c>
       <c r="C34" s="11">
@@ -2478,7 +2394,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="65" t="n">
+      <c r="B35" s="67" t="n">
         <v>6.35</v>
       </c>
       <c r="C35" s="11">
@@ -2503,7 +2419,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="65" t="n">
+      <c r="B36" s="67" t="n">
         <v>6.75</v>
       </c>
       <c r="C36" s="11">
@@ -2528,7 +2444,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="65" t="n">
+      <c r="B37" s="67" t="n">
         <v>7.25</v>
       </c>
       <c r="C37" s="11">
@@ -2569,29 +2485,29 @@
       <c r="J39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="30" t="inlineStr">
+      <c r="B40" s="32" t="inlineStr">
         <is>
           <t>30-yr mortgage rate  \  competition premium (pp of gross ASP)</t>
         </is>
       </c>
-      <c r="C40" s="65" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" s="65" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E40" s="65" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F40" s="65" t="n">
-        <v>6</v>
-      </c>
-      <c r="G40" s="65" t="n">
-        <v>7.5</v>
+      <c r="C40" s="67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D40" s="67" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E40" s="67" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F40" s="67" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G40" s="67" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="65" t="n">
+      <c r="B41" s="67" t="n">
         <v>5.5</v>
       </c>
       <c r="C41" s="16">
@@ -2621,7 +2537,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="65" t="n">
+      <c r="B42" s="67" t="n">
         <v>6</v>
       </c>
       <c r="C42" s="16">
@@ -2646,7 +2562,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="65" t="n">
+      <c r="B43" s="67" t="n">
         <v>6.35</v>
       </c>
       <c r="C43" s="16">
@@ -2657,7 +2573,7 @@
         <f>1-($C$6*$C$10+$C$7*$C$11+$C$12*(1-$C$28/100)+$C$25)/((($C$6*($C$8*(1-($C$17+$C$18*MAX(0,$B$43-$C$16)+$C$15)/100)))+$C$12*(1-$C$29/100))+(($C$7*($C$9*(1-($C$19+$C$20*MAX(0,$B$43-$C$16)+D$40)/100)))+$C$12*$C$29/100))</f>
         <v/>
       </c>
-      <c r="E43" s="63">
+      <c r="E43" s="65">
         <f>1-($C$6*$C$10+$C$7*$C$11+$C$12*(1-$C$28/100)+$C$25)/((($C$6*($C$8*(1-($C$17+$C$18*MAX(0,$B$43-$C$16)+$C$15)/100)))+$C$12*(1-$C$29/100))+(($C$7*($C$9*(1-($C$19+$C$20*MAX(0,$B$43-$C$16)+E$40)/100)))+$C$12*$C$29/100))</f>
         <v/>
       </c>
@@ -2671,7 +2587,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="65" t="n">
+      <c r="B44" s="67" t="n">
         <v>6.75</v>
       </c>
       <c r="C44" s="16">
@@ -2696,7 +2612,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="65" t="n">
+      <c r="B45" s="67" t="n">
         <v>7.25</v>
       </c>
       <c r="C45" s="16">
@@ -2802,7 +2718,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>UNDERWEIGHT</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2729,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
@@ -2982,7 +2898,7 @@
         <v/>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="H23" s="11">
         <f>C23*G23</f>
@@ -2990,18 +2906,18 @@
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>Cash-flow view, and the only method here not anchored to what peers trade at. Says the earnings recovery does not reach shareholders because land absorbs it.</t>
+          <t>What the business earns, and what is left for shareholders after land absorbs its share. Weighted more heavily because it is the only method that prices the return gap.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Relative multiple — regression P/B on 2027E ROE</t>
+          <t>Peer median P/B on Sep-2027E book</t>
         </is>
       </c>
       <c r="C24" s="11">
-        <f>Comps!H37</f>
+        <f>Comps!H35</f>
         <v/>
       </c>
       <c r="E24" s="16">
@@ -3017,52 +2933,41 @@
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>Peer-pricing view. Because P/B = P/E x ROE is an identity, this and an earnings multiple are ONE method, not two, and are not weighted separately. Peer median P/E on 2027E EPS ($197) and unadjusted peer median P/B ($190) sit on the Comps sheet as cross-checks on this line, not as extra weights.</t>
+          <t>What the market pays other builders for a dollar of book. The multiple comes from the comp set, not from MHO, which is what makes this independent of the DCF and able to disagree with the current price.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>Justified P/B (residual income)</t>
-        </is>
-      </c>
-      <c r="C25" s="11">
-        <f>Comps!H38</f>
-        <v/>
-      </c>
-      <c r="E25" s="16">
-        <f>C25/C8-1</f>
-        <v/>
-      </c>
-      <c r="G25" s="17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H25" s="11">
-        <f>C25*G25</f>
-        <v/>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>Absolute view: a business earning roughly its cost of equity is worth roughly book. Agrees with the DCF, independent of peer pricing.</t>
-        </is>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Weighted value per share</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="G25" s="20">
+        <f>SUM(G23:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="21">
+        <f>SUM(H23:H24)</f>
+        <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>Weighted value per share</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="n"/>
-      <c r="E26" s="19" t="n"/>
-      <c r="G26" s="20">
-        <f>SUM(G23:G25)</f>
-        <v/>
-      </c>
-      <c r="H26" s="21">
-        <f>SUM(H23:H25)</f>
-        <v/>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Cross-check: probability-weighted value (25/50/25 across the scenarios below)</t>
+        </is>
+      </c>
+      <c r="H26" s="23">
+        <f>0.25*F30+0.5*F31+0.25*F32</f>
+        <v/>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>Not a second price target — a test of the rating. A probability-weighted value below the share price is what makes this a Sell rather than a Hold.</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="15.5" customHeight="1">
@@ -3118,24 +3023,24 @@
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>17.33356857813424</v>
+        <v>16.19294706284738</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>28.54431496860798</v>
+        <v>26.14913067485417</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>0.1354557749811998</v>
-      </c>
-      <c r="F30" s="23" t="n">
+        <v>0.1258466063643327</v>
+      </c>
+      <c r="F30" s="25" t="n">
         <v>205</v>
       </c>
-      <c r="G30" s="24">
+      <c r="G30" s="26">
         <f>F30/$C$8-1</f>
         <v/>
       </c>
@@ -3146,24 +3051,24 @@
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C31" s="26" t="n">
-        <v>14.78186850572908</v>
-      </c>
-      <c r="D31" s="26" t="n">
-        <v>24.24190177417711</v>
-      </c>
-      <c r="E31" s="27" t="n">
-        <v>0.1182998210252073</v>
-      </c>
-      <c r="F31" s="28" t="n">
+      <c r="C31" s="28" t="n">
+        <v>14.06119322936485</v>
+      </c>
+      <c r="D31" s="28" t="n">
+        <v>21.15692798587284</v>
+      </c>
+      <c r="E31" s="29" t="n">
+        <v>0.1084713042026645</v>
+      </c>
+      <c r="F31" s="30" t="n">
         <v>160</v>
       </c>
-      <c r="G31" s="29">
+      <c r="G31" s="31">
         <f>F31/$C$8-1</f>
         <v/>
       </c>
@@ -3174,24 +3079,24 @@
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>9.175868745497866</v>
+        <v>9.529085045303544</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>9.888775068968926</v>
+        <v>9.886166281029503</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>0.06441835649972795</v>
-      </c>
-      <c r="F32" s="23" t="n">
+        <v>0.06694434902229758</v>
+      </c>
+      <c r="F32" s="25" t="n">
         <v>95</v>
       </c>
-      <c r="G32" s="24">
+      <c r="G32" s="26">
         <f>F32/$C$8-1</f>
         <v/>
       </c>
@@ -3218,32 +3123,32 @@
       <c r="J34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="30" t="inlineStr">
+      <c r="B35" s="32" t="inlineStr">
         <is>
           <t>($ in millions except per-share)</t>
         </is>
       </c>
-      <c r="C35" s="31" t="inlineStr">
+      <c r="C35" s="33" t="inlineStr">
         <is>
           <t>2024A</t>
         </is>
       </c>
-      <c r="D35" s="31" t="inlineStr">
+      <c r="D35" s="33" t="inlineStr">
         <is>
           <t>2025A</t>
         </is>
       </c>
-      <c r="E35" s="31" t="inlineStr">
+      <c r="E35" s="33" t="inlineStr">
         <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="F35" s="31" t="inlineStr">
+      <c r="F35" s="33" t="inlineStr">
         <is>
           <t>2027E</t>
         </is>
       </c>
-      <c r="G35" s="31" t="inlineStr">
+      <c r="G35" s="33" t="inlineStr">
         <is>
           <t>2028E</t>
         </is>
@@ -3309,23 +3214,23 @@
           <t>Gross margin — homebuilding (%)</t>
         </is>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="34">
         <f>1-IS!D14/(IS!D8+IS!D9)</f>
         <v/>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="34">
         <f>1-IS!E14/(IS!E8+IS!E9)</f>
         <v/>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="34">
         <f>1-IS!F14/(IS!F8+IS!F9)</f>
         <v/>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="34">
         <f>1-IS!G14/(IS!G8+IS!G9)</f>
         <v/>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="34">
         <f>1-IS!H14/(IS!H8+IS!H9)</f>
         <v/>
       </c>
@@ -3363,23 +3268,23 @@
           <t>Southern operating margin (%)</t>
         </is>
       </c>
-      <c r="C40" s="32">
+      <c r="C40" s="34">
         <f>IS!D42/IS!D9</f>
         <v/>
       </c>
-      <c r="D40" s="32">
+      <c r="D40" s="34">
         <f>IS!E42/IS!E9</f>
         <v/>
       </c>
-      <c r="E40" s="32">
+      <c r="E40" s="34">
         <f>IS!F42/IS!F9</f>
         <v/>
       </c>
-      <c r="F40" s="32">
+      <c r="F40" s="34">
         <f>IS!G42/IS!G9</f>
         <v/>
       </c>
-      <c r="G40" s="32">
+      <c r="G40" s="34">
         <f>IS!H42/IS!H9</f>
         <v/>
       </c>
@@ -3390,23 +3295,23 @@
           <t>Northern operating margin (%)</t>
         </is>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="34">
         <f>IS!D41/IS!D8</f>
         <v/>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="34">
         <f>IS!E41/IS!E8</f>
         <v/>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="34">
         <f>IS!F41/IS!F8</f>
         <v/>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="34">
         <f>IS!G41/IS!G8</f>
         <v/>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="34">
         <f>IS!H41/IS!H8</f>
         <v/>
       </c>
@@ -3417,23 +3322,23 @@
           <t>Diluted EPS ($)</t>
         </is>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="35">
         <f>IS!D37</f>
         <v/>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="35">
         <f>IS!E37</f>
         <v/>
       </c>
-      <c r="E42" s="33">
+      <c r="E42" s="35">
         <f>IS!F37</f>
         <v/>
       </c>
-      <c r="F42" s="33">
+      <c r="F42" s="35">
         <f>IS!G37</f>
         <v/>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="35">
         <f>IS!H37</f>
         <v/>
       </c>
@@ -3471,23 +3376,23 @@
           <t>Return on equity (%)</t>
         </is>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="34">
         <f>BS!D29</f>
         <v/>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="34">
         <f>BS!E29</f>
         <v/>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="34">
         <f>BS!F29</f>
         <v/>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="34">
         <f>BS!G29</f>
         <v/>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="34">
         <f>BS!H29</f>
         <v/>
       </c>
@@ -3563,47 +3468,47 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>DRIVER</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>2023A</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>2024A</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>2025A</t>
         </is>
       </c>
-      <c r="F5" s="35" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="G5" s="35" t="inlineStr">
+      <c r="G5" s="37" t="inlineStr">
         <is>
           <t>2027E</t>
         </is>
       </c>
-      <c r="H5" s="35" t="inlineStr">
+      <c r="H5" s="37" t="inlineStr">
         <is>
           <t>2028E</t>
         </is>
       </c>
-      <c r="I5" s="35" t="inlineStr">
+      <c r="I5" s="37" t="inlineStr">
         <is>
           <t>2029E</t>
         </is>
       </c>
-      <c r="J5" s="35" t="inlineStr">
+      <c r="J5" s="37" t="inlineStr">
         <is>
           <t>2030E</t>
         </is>
@@ -3626,33 +3531,33 @@
       <c r="J7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>30-yr fixed mortgage rate (annual avg, %)</t>
         </is>
       </c>
-      <c r="C8" s="37" t="n">
+      <c r="C8" s="39" t="n">
         <v>6.81</v>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="39" t="n">
         <v>6.8</v>
       </c>
-      <c r="E8" s="37" t="n">
+      <c r="E8" s="39" t="n">
         <v>6.72</v>
       </c>
-      <c r="F8" s="37" t="n">
+      <c r="F8" s="39" t="n">
         <v>6.65</v>
       </c>
-      <c r="G8" s="37" t="n">
+      <c r="G8" s="39" t="n">
         <v>6.35</v>
       </c>
-      <c r="H8" s="37" t="n">
+      <c r="H8" s="39" t="n">
         <v>6.1</v>
       </c>
-      <c r="I8" s="37" t="n">
+      <c r="I8" s="39" t="n">
         <v>5.95</v>
       </c>
-      <c r="J8" s="37" t="n">
+      <c r="J8" s="39" t="n">
         <v>5.9</v>
       </c>
       <c r="L8" s="9" t="inlineStr">
@@ -3667,7 +3572,7 @@
           <t>Neutral mortgage rate (%)</t>
         </is>
       </c>
-      <c r="C9" s="37" t="n">
+      <c r="C9" s="39" t="n">
         <v>5.5</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -3698,8 +3603,8 @@
           <t>Northern — base incentive (% of gross ASP)</t>
         </is>
       </c>
-      <c r="C12" s="37" t="n">
-        <v>2.5</v>
+      <c r="C12" s="39" t="n">
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -3708,39 +3613,39 @@
           <t>Northern — rate slope (pp per 100bp above neutral)</t>
         </is>
       </c>
-      <c r="C13" s="38" t="n">
+      <c r="C13" s="40" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="38" t="inlineStr">
         <is>
           <t>Northern — competition premium (pp)</t>
         </is>
       </c>
-      <c r="C14" s="37" t="n">
+      <c r="C14" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="37" t="n">
+      <c r="D14" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G14" s="37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H14" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="37" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J14" s="37" t="n">
-        <v>0.5</v>
+      <c r="E14" s="39" t="n">
+        <v>1.209</v>
+      </c>
+      <c r="F14" s="39" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="G14" s="39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H14" s="39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I14" s="39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J14" s="39" t="n">
+        <v>2.65</v>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
@@ -3754,8 +3659,8 @@
           <t>Southern — base incentive (% of gross ASP)</t>
         </is>
       </c>
-      <c r="C15" s="37" t="n">
-        <v>3</v>
+      <c r="C15" s="39" t="n">
+        <v>1.944</v>
       </c>
     </row>
     <row r="16">
@@ -3764,39 +3669,39 @@
           <t>Southern — rate slope (pp per 100bp above neutral)</t>
         </is>
       </c>
-      <c r="C16" s="38" t="n">
+      <c r="C16" s="40" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="36" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>Southern — competition premium (pp)</t>
         </is>
       </c>
-      <c r="C17" s="37" t="n">
+      <c r="C17" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="37" t="n">
+      <c r="D17" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F17" s="37" t="n">
-        <v>6</v>
-      </c>
-      <c r="G17" s="37" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H17" s="37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I17" s="37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J17" s="37" t="n">
-        <v>2</v>
+      <c r="E17" s="39" t="n">
+        <v>1.972</v>
+      </c>
+      <c r="F17" s="39" t="n">
+        <v>4.371</v>
+      </c>
+      <c r="G17" s="39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H17" s="39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I17" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="39" t="n">
+        <v>2.8</v>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
@@ -3821,68 +3726,68 @@
       <c r="J19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="36" t="inlineStr">
+      <c r="B20" s="38" t="inlineStr">
         <is>
           <t>Deliveries growth — Northern (%)</t>
         </is>
       </c>
-      <c r="F20" s="37" t="n">
+      <c r="F20" s="39" t="n">
         <v>-3.9</v>
       </c>
-      <c r="G20" s="37" t="n">
+      <c r="G20" s="39" t="n">
         <v>3.5</v>
       </c>
-      <c r="H20" s="37" t="n">
+      <c r="H20" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="37" t="n">
+      <c r="I20" s="39" t="n">
         <v>3.25</v>
       </c>
-      <c r="J20" s="37" t="n">
+      <c r="J20" s="39" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="36" t="inlineStr">
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t>Deliveries growth — Southern (%)</t>
         </is>
       </c>
-      <c r="F21" s="37" t="n">
+      <c r="F21" s="39" t="n">
         <v>-4.3</v>
       </c>
-      <c r="G21" s="37" t="n">
+      <c r="G21" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="H21" s="37" t="n">
+      <c r="H21" s="39" t="n">
         <v>5.5</v>
       </c>
-      <c r="I21" s="37" t="n">
+      <c r="I21" s="39" t="n">
         <v>4.25</v>
       </c>
-      <c r="J21" s="37" t="n">
+      <c r="J21" s="39" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="38" t="inlineStr">
         <is>
           <t>Gross ASP growth — Northern (%)</t>
         </is>
       </c>
-      <c r="F22" s="37" t="n">
+      <c r="F22" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="37" t="n">
+      <c r="G22" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="37" t="n">
+      <c r="H22" s="39" t="n">
         <v>2.25</v>
       </c>
-      <c r="I22" s="37" t="n">
+      <c r="I22" s="39" t="n">
         <v>2.5</v>
       </c>
-      <c r="J22" s="37" t="n">
+      <c r="J22" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -3892,68 +3797,68 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="36" t="inlineStr">
+      <c r="B23" s="38" t="inlineStr">
         <is>
           <t>Gross ASP growth — Southern (%)</t>
         </is>
       </c>
-      <c r="F23" s="37" t="n">
+      <c r="F23" s="39" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G23" s="37" t="n">
+      <c r="G23" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="37" t="n">
+      <c r="H23" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="37" t="n">
+      <c r="I23" s="39" t="n">
         <v>2.25</v>
       </c>
-      <c r="J23" s="37" t="n">
+      <c r="J23" s="39" t="n">
         <v>2.25</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="36" t="inlineStr">
+      <c r="B24" s="38" t="inlineStr">
         <is>
           <t>Cost per home growth — Northern (%)</t>
         </is>
       </c>
-      <c r="F24" s="37" t="n">
+      <c r="F24" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="37" t="n">
+      <c r="G24" s="39" t="n">
         <v>2.2</v>
       </c>
-      <c r="H24" s="37" t="n">
+      <c r="H24" s="39" t="n">
         <v>2.4</v>
       </c>
-      <c r="I24" s="37" t="n">
+      <c r="I24" s="39" t="n">
         <v>2.5</v>
       </c>
-      <c r="J24" s="37" t="n">
+      <c r="J24" s="39" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="36" t="inlineStr">
+      <c r="B25" s="38" t="inlineStr">
         <is>
           <t>Cost per home growth — Southern (%)</t>
         </is>
       </c>
-      <c r="F25" s="37" t="n">
+      <c r="F25" s="39" t="n">
         <v>-0.3</v>
       </c>
-      <c r="G25" s="37" t="n">
+      <c r="G25" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="37" t="n">
+      <c r="H25" s="39" t="n">
         <v>2.3</v>
       </c>
-      <c r="I25" s="37" t="n">
+      <c r="I25" s="39" t="n">
         <v>2.5</v>
       </c>
-      <c r="J25" s="37" t="n">
+      <c r="J25" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="L25" s="9" t="inlineStr">
@@ -3979,112 +3884,112 @@
       <c r="J27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="36" t="inlineStr">
+      <c r="B28" s="38" t="inlineStr">
         <is>
           <t>Land sale revenue ($000)</t>
         </is>
       </c>
-      <c r="F28" s="39" t="n">
+      <c r="F28" s="41" t="n">
         <v>22000</v>
       </c>
-      <c r="G28" s="39" t="n">
+      <c r="G28" s="41" t="n">
         <v>24000</v>
       </c>
-      <c r="H28" s="39" t="n">
+      <c r="H28" s="41" t="n">
         <v>26000</v>
       </c>
-      <c r="I28" s="39" t="n">
+      <c r="I28" s="41" t="n">
         <v>28000</v>
       </c>
-      <c r="J28" s="39" t="n">
+      <c r="J28" s="41" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="36" t="inlineStr">
+      <c r="B29" s="38" t="inlineStr">
         <is>
           <t>Financial services revenue growth (%)</t>
         </is>
       </c>
-      <c r="F29" s="37" t="n">
+      <c r="F29" s="39" t="n">
         <v>1.5</v>
       </c>
-      <c r="G29" s="37" t="n">
+      <c r="G29" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="37" t="n">
+      <c r="H29" s="39" t="n">
         <v>5.5</v>
       </c>
-      <c r="I29" s="37" t="n">
+      <c r="I29" s="39" t="n">
         <v>4.5</v>
       </c>
-      <c r="J29" s="37" t="n">
+      <c r="J29" s="39" t="n">
         <v>4.5</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="36" t="inlineStr">
+      <c r="B30" s="38" t="inlineStr">
         <is>
           <t>Selling expense (% of homebuilding revenue)</t>
         </is>
       </c>
-      <c r="F30" s="37" t="n">
+      <c r="F30" s="39" t="n">
         <v>6.2</v>
       </c>
-      <c r="G30" s="37" t="n">
+      <c r="G30" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="H30" s="37" t="n">
+      <c r="H30" s="39" t="n">
         <v>5.8</v>
       </c>
-      <c r="I30" s="37" t="n">
+      <c r="I30" s="39" t="n">
         <v>5.7</v>
       </c>
-      <c r="J30" s="37" t="n">
+      <c r="J30" s="39" t="n">
         <v>5.65</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="36" t="inlineStr">
+      <c r="B31" s="38" t="inlineStr">
         <is>
           <t>Homebuilding G&amp;A (% of homebuilding revenue)</t>
         </is>
       </c>
-      <c r="F31" s="37" t="n">
+      <c r="F31" s="39" t="n">
         <v>2.8</v>
       </c>
-      <c r="G31" s="37" t="n">
+      <c r="G31" s="39" t="n">
         <v>2.72</v>
       </c>
-      <c r="H31" s="37" t="n">
+      <c r="H31" s="39" t="n">
         <v>2.66</v>
       </c>
-      <c r="I31" s="37" t="n">
+      <c r="I31" s="39" t="n">
         <v>2.63</v>
       </c>
-      <c r="J31" s="37" t="n">
+      <c r="J31" s="39" t="n">
         <v>2.6</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="36" t="inlineStr">
+      <c r="B32" s="38" t="inlineStr">
         <is>
           <t>Corporate / unallocated ($000)</t>
         </is>
       </c>
-      <c r="F32" s="39" t="n">
+      <c r="F32" s="41" t="n">
         <v>-93000</v>
       </c>
-      <c r="G32" s="39" t="n">
+      <c r="G32" s="41" t="n">
         <v>-96500</v>
       </c>
-      <c r="H32" s="39" t="n">
+      <c r="H32" s="41" t="n">
         <v>-100500</v>
       </c>
-      <c r="I32" s="39" t="n">
+      <c r="I32" s="41" t="n">
         <v>-104500</v>
       </c>
-      <c r="J32" s="39" t="n">
+      <c r="J32" s="41" t="n">
         <v>-108500</v>
       </c>
       <c r="L32" s="9" t="inlineStr">
@@ -4094,24 +3999,24 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="36" t="inlineStr">
+      <c r="B33" s="38" t="inlineStr">
         <is>
           <t>Inventory impairment &amp; write-offs ($000)</t>
         </is>
       </c>
-      <c r="F33" s="39" t="n">
+      <c r="F33" s="41" t="n">
         <v>16000</v>
       </c>
-      <c r="G33" s="39" t="n">
+      <c r="G33" s="41" t="n">
         <v>9000</v>
       </c>
-      <c r="H33" s="39" t="n">
+      <c r="H33" s="41" t="n">
         <v>7000</v>
       </c>
-      <c r="I33" s="39" t="n">
+      <c r="I33" s="41" t="n">
         <v>7000</v>
       </c>
-      <c r="J33" s="39" t="n">
+      <c r="J33" s="41" t="n">
         <v>7000</v>
       </c>
       <c r="L33" s="9" t="inlineStr">
@@ -4121,24 +4026,24 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="36" t="inlineStr">
+      <c r="B34" s="38" t="inlineStr">
         <is>
           <t>Net interest income ($000)</t>
         </is>
       </c>
-      <c r="F34" s="39" t="n">
+      <c r="F34" s="41" t="n">
         <v>18000</v>
       </c>
-      <c r="G34" s="39" t="n">
+      <c r="G34" s="41" t="n">
         <v>16000</v>
       </c>
-      <c r="H34" s="39" t="n">
+      <c r="H34" s="41" t="n">
         <v>15000</v>
       </c>
-      <c r="I34" s="39" t="n">
+      <c r="I34" s="41" t="n">
         <v>15000</v>
       </c>
-      <c r="J34" s="39" t="n">
+      <c r="J34" s="41" t="n">
         <v>16000</v>
       </c>
     </row>
@@ -4148,7 +4053,7 @@
           <t>Land sale gross margin (%)</t>
         </is>
       </c>
-      <c r="C35" s="37" t="n">
+      <c r="C35" s="39" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4158,7 +4063,7 @@
           <t>Share of land revenue in Southern (%)</t>
         </is>
       </c>
-      <c r="C36" s="40" t="n">
+      <c r="C36" s="42" t="n">
         <v>65</v>
       </c>
     </row>
@@ -4168,7 +4073,7 @@
           <t>Financial services pre-tax margin (%)</t>
         </is>
       </c>
-      <c r="C37" s="37" t="n">
+      <c r="C37" s="39" t="n">
         <v>54.5</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4183,7 +4088,7 @@
           <t>Effective tax rate (%)</t>
         </is>
       </c>
-      <c r="C38" s="37" t="n">
+      <c r="C38" s="39" t="n">
         <v>23.5</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -4209,24 +4114,24 @@
       <c r="J40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="36" t="inlineStr">
+      <c r="B41" s="38" t="inlineStr">
         <is>
           <t>Inventory turns (homebuilding revenue / ending inventory)</t>
         </is>
       </c>
-      <c r="F41" s="38" t="n">
+      <c r="F41" s="40" t="n">
         <v>1.2</v>
       </c>
-      <c r="G41" s="38" t="n">
+      <c r="G41" s="40" t="n">
         <v>1.22</v>
       </c>
-      <c r="H41" s="38" t="n">
+      <c r="H41" s="40" t="n">
         <v>1.24</v>
       </c>
-      <c r="I41" s="38" t="n">
+      <c r="I41" s="40" t="n">
         <v>1.25</v>
       </c>
-      <c r="J41" s="38" t="n">
+      <c r="J41" s="40" t="n">
         <v>1.26</v>
       </c>
       <c r="L41" s="9" t="inlineStr">
@@ -4236,46 +4141,46 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="36" t="inlineStr">
+      <c r="B42" s="38" t="inlineStr">
         <is>
           <t>Other operating assets (% of revenue)</t>
         </is>
       </c>
-      <c r="F42" s="37" t="n">
+      <c r="F42" s="39" t="n">
         <v>14.3</v>
       </c>
-      <c r="G42" s="37" t="n">
+      <c r="G42" s="39" t="n">
         <v>14.25</v>
       </c>
-      <c r="H42" s="37" t="n">
+      <c r="H42" s="39" t="n">
         <v>14.2</v>
       </c>
-      <c r="I42" s="37" t="n">
+      <c r="I42" s="39" t="n">
         <v>14.15</v>
       </c>
-      <c r="J42" s="37" t="n">
+      <c r="J42" s="39" t="n">
         <v>14.1</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="36" t="inlineStr">
+      <c r="B43" s="38" t="inlineStr">
         <is>
           <t>Other liabilities (% of revenue)</t>
         </is>
       </c>
-      <c r="F43" s="37" t="n">
+      <c r="F43" s="39" t="n">
         <v>14.45</v>
       </c>
-      <c r="G43" s="37" t="n">
+      <c r="G43" s="39" t="n">
         <v>14.5</v>
       </c>
-      <c r="H43" s="37" t="n">
+      <c r="H43" s="39" t="n">
         <v>14.55</v>
       </c>
-      <c r="I43" s="37" t="n">
+      <c r="I43" s="39" t="n">
         <v>14.55</v>
       </c>
-      <c r="J43" s="37" t="n">
+      <c r="J43" s="39" t="n">
         <v>14.55</v>
       </c>
       <c r="L43" s="9" t="inlineStr">
@@ -4285,90 +4190,90 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="36" t="inlineStr">
+      <c r="B44" s="38" t="inlineStr">
         <is>
           <t>Capital expenditure ($000)</t>
         </is>
       </c>
-      <c r="F44" s="39" t="n">
+      <c r="F44" s="41" t="n">
         <v>11000</v>
       </c>
-      <c r="G44" s="39" t="n">
+      <c r="G44" s="41" t="n">
         <v>11500</v>
       </c>
-      <c r="H44" s="39" t="n">
+      <c r="H44" s="41" t="n">
         <v>12000</v>
       </c>
-      <c r="I44" s="39" t="n">
+      <c r="I44" s="41" t="n">
         <v>12500</v>
       </c>
-      <c r="J44" s="39" t="n">
+      <c r="J44" s="41" t="n">
         <v>13000</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="36" t="inlineStr">
+      <c r="B45" s="38" t="inlineStr">
         <is>
           <t>Depreciation &amp; amortisation ($000)</t>
         </is>
       </c>
-      <c r="F45" s="39" t="n">
+      <c r="F45" s="41" t="n">
         <v>20000</v>
       </c>
-      <c r="G45" s="39" t="n">
+      <c r="G45" s="41" t="n">
         <v>21000</v>
       </c>
-      <c r="H45" s="39" t="n">
+      <c r="H45" s="41" t="n">
         <v>22000</v>
       </c>
-      <c r="I45" s="39" t="n">
+      <c r="I45" s="41" t="n">
         <v>23000</v>
       </c>
-      <c r="J45" s="39" t="n">
+      <c r="J45" s="41" t="n">
         <v>24000</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="36" t="inlineStr">
+      <c r="B46" s="38" t="inlineStr">
         <is>
           <t>Stock-based compensation ($000)</t>
         </is>
       </c>
-      <c r="F46" s="39" t="n">
+      <c r="F46" s="41" t="n">
         <v>17500</v>
       </c>
-      <c r="G46" s="39" t="n">
+      <c r="G46" s="41" t="n">
         <v>18000</v>
       </c>
-      <c r="H46" s="39" t="n">
+      <c r="H46" s="41" t="n">
         <v>18500</v>
       </c>
-      <c r="I46" s="39" t="n">
+      <c r="I46" s="41" t="n">
         <v>19000</v>
       </c>
-      <c r="J46" s="39" t="n">
+      <c r="J46" s="41" t="n">
         <v>19500</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="36" t="inlineStr">
+      <c r="B47" s="38" t="inlineStr">
         <is>
           <t>Share repurchase ($000)</t>
         </is>
       </c>
-      <c r="F47" s="39" t="n">
+      <c r="F47" s="41" t="n">
         <v>185000</v>
       </c>
-      <c r="G47" s="39" t="n">
+      <c r="G47" s="41" t="n">
         <v>185000</v>
       </c>
-      <c r="H47" s="39" t="n">
+      <c r="H47" s="41" t="n">
         <v>185000</v>
       </c>
-      <c r="I47" s="39" t="n">
+      <c r="I47" s="41" t="n">
         <v>185000</v>
       </c>
-      <c r="J47" s="39" t="n">
+      <c r="J47" s="41" t="n">
         <v>185000</v>
       </c>
       <c r="L47" s="9" t="inlineStr">
@@ -4378,68 +4283,68 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="36" t="inlineStr">
+      <c r="B48" s="38" t="inlineStr">
         <is>
           <t>Average repurchase price ($)</t>
         </is>
       </c>
-      <c r="F48" s="41" t="n">
+      <c r="F48" s="43" t="n">
         <v>150</v>
       </c>
-      <c r="G48" s="41" t="n">
+      <c r="G48" s="43" t="n">
         <v>161</v>
       </c>
-      <c r="H48" s="41" t="n">
+      <c r="H48" s="43" t="n">
         <v>174</v>
       </c>
-      <c r="I48" s="41" t="n">
+      <c r="I48" s="43" t="n">
         <v>187</v>
       </c>
-      <c r="J48" s="41" t="n">
+      <c r="J48" s="43" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="36" t="inlineStr">
+      <c r="B49" s="38" t="inlineStr">
         <is>
           <t>Option / RSU issuance (000 shares)</t>
         </is>
       </c>
-      <c r="F49" s="39" t="n">
+      <c r="F49" s="41" t="n">
         <v>150</v>
       </c>
-      <c r="G49" s="39" t="n">
+      <c r="G49" s="41" t="n">
         <v>150</v>
       </c>
-      <c r="H49" s="39" t="n">
+      <c r="H49" s="41" t="n">
         <v>150</v>
       </c>
-      <c r="I49" s="39" t="n">
+      <c r="I49" s="41" t="n">
         <v>150</v>
       </c>
-      <c r="J49" s="39" t="n">
+      <c r="J49" s="41" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="36" t="inlineStr">
+      <c r="B50" s="38" t="inlineStr">
         <is>
           <t>Homebuilding debt ($000)</t>
         </is>
       </c>
-      <c r="F50" s="39" t="n">
+      <c r="F50" s="41" t="n">
         <v>696500</v>
       </c>
-      <c r="G50" s="39" t="n">
+      <c r="G50" s="41" t="n">
         <v>696500</v>
       </c>
-      <c r="H50" s="39" t="n">
+      <c r="H50" s="41" t="n">
         <v>696500</v>
       </c>
-      <c r="I50" s="39" t="n">
+      <c r="I50" s="41" t="n">
         <v>550000</v>
       </c>
-      <c r="J50" s="39" t="n">
+      <c r="J50" s="41" t="n">
         <v>550000</v>
       </c>
       <c r="L50" s="9" t="inlineStr">
@@ -4449,24 +4354,24 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="36" t="inlineStr">
+      <c r="B51" s="38" t="inlineStr">
         <is>
           <t>Financial services debt ($000)</t>
         </is>
       </c>
-      <c r="F51" s="39" t="n">
+      <c r="F51" s="41" t="n">
         <v>290000</v>
       </c>
-      <c r="G51" s="39" t="n">
+      <c r="G51" s="41" t="n">
         <v>305000</v>
       </c>
-      <c r="H51" s="39" t="n">
+      <c r="H51" s="41" t="n">
         <v>322000</v>
       </c>
-      <c r="I51" s="39" t="n">
+      <c r="I51" s="41" t="n">
         <v>336000</v>
       </c>
-      <c r="J51" s="39" t="n">
+      <c r="J51" s="41" t="n">
         <v>351000</v>
       </c>
       <c r="L51" s="9" t="inlineStr">
@@ -4481,7 +4386,7 @@
           <t>Property &amp; equipment at 31-Dec-2025 ($000)</t>
         </is>
       </c>
-      <c r="C52" s="39" t="n">
+      <c r="C52" s="41" t="n">
         <v>70000</v>
       </c>
     </row>
@@ -4507,7 +4412,7 @@
           <t>Risk-free rate — 10-yr UST (%)</t>
         </is>
       </c>
-      <c r="C55" s="37" t="n">
+      <c r="C55" s="39" t="n">
         <v>4.79</v>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -4522,7 +4427,7 @@
           <t>Equity risk premium (%)</t>
         </is>
       </c>
-      <c r="C56" s="37" t="n">
+      <c r="C56" s="39" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4532,12 +4437,12 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="C57" s="38" t="n">
-        <v>1.35</v>
+      <c r="C57" s="40" t="n">
+        <v>1.41</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Homebuilders cluster 1.2–1.5; MHO at the mid-cap end.</t>
+          <t>Blume-adjusted: 0.67 x the published 5-yr raw beta of 1.61, + 0.33 x 1.0. Raw historical betas are noisy and mean-revert, which is why Bloomberg reports the adjusted figure.</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4452,7 @@
           <t>Pre-tax cost of debt (%)</t>
         </is>
       </c>
-      <c r="C58" s="37" t="n">
+      <c r="C58" s="39" t="n">
         <v>6.25</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -4562,7 +4467,7 @@
           <t>Terminal growth rate (%)</t>
         </is>
       </c>
-      <c r="C59" s="37" t="n">
+      <c r="C59" s="39" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -4572,7 +4477,7 @@
           <t>Share price ($)</t>
         </is>
       </c>
-      <c r="C60" s="23" t="n">
+      <c r="C60" s="25" t="n">
         <v>148.26</v>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -4587,7 +4492,7 @@
           <t>Shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C61" s="39" t="n">
+      <c r="C61" s="41" t="n">
         <v>25276</v>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -4640,47 +4545,47 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>($ in thousands unless noted)</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>2023A</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>2024A</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>2025A</t>
         </is>
       </c>
-      <c r="F5" s="35" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="G5" s="35" t="inlineStr">
+      <c r="G5" s="37" t="inlineStr">
         <is>
           <t>2027E</t>
         </is>
       </c>
-      <c r="H5" s="35" t="inlineStr">
+      <c r="H5" s="37" t="inlineStr">
         <is>
           <t>2028E</t>
         </is>
       </c>
-      <c r="I5" s="35" t="inlineStr">
+      <c r="I5" s="37" t="inlineStr">
         <is>
           <t>2029E</t>
         </is>
       </c>
-      <c r="J5" s="35" t="inlineStr">
+      <c r="J5" s="37" t="inlineStr">
         <is>
           <t>2030E</t>
         </is>
@@ -4703,18 +4608,18 @@
       <c r="J7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Homes delivered — Northern</t>
         </is>
       </c>
-      <c r="C8" s="39" t="n">
+      <c r="C8" s="41" t="n">
         <v>3169</v>
       </c>
-      <c r="D8" s="39" t="n">
+      <c r="D8" s="41" t="n">
         <v>3873</v>
       </c>
-      <c r="E8" s="39" t="n">
+      <c r="E8" s="41" t="n">
         <v>3716</v>
       </c>
       <c r="L8" s="9" t="inlineStr">
@@ -4724,36 +4629,36 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>Homes delivered — Southern</t>
         </is>
       </c>
-      <c r="C9" s="39" t="n">
+      <c r="C9" s="41" t="n">
         <v>4943</v>
       </c>
-      <c r="D9" s="39" t="n">
+      <c r="D9" s="41" t="n">
         <v>5182</v>
       </c>
-      <c r="E9" s="39" t="n">
+      <c r="E9" s="41" t="n">
         <v>5205</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B10" s="44" t="inlineStr">
         <is>
           <t>Homes delivered — total</t>
         </is>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="45">
         <f>C8+C9</f>
         <v/>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="45">
         <f>D8+D9</f>
         <v/>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="45">
         <f>E8+E9</f>
         <v/>
       </c>
@@ -4764,50 +4669,50 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>New contracts — Northern</t>
         </is>
       </c>
-      <c r="C11" s="39" t="n">
+      <c r="C11" s="41" t="n">
         <v>3361</v>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D11" s="41" t="n">
         <v>3761</v>
       </c>
-      <c r="E11" s="39" t="n">
+      <c r="E11" s="41" t="n">
         <v>3416</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>New contracts — Southern</t>
         </is>
       </c>
-      <c r="C12" s="39" t="n">
+      <c r="C12" s="41" t="n">
         <v>4616</v>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D12" s="41" t="n">
         <v>4823</v>
       </c>
-      <c r="E12" s="39" t="n">
+      <c r="E12" s="41" t="n">
         <v>4783</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>Backlog units — year end</t>
         </is>
       </c>
-      <c r="C13" s="39" t="n">
+      <c r="C13" s="41" t="n">
         <v>3002</v>
       </c>
-      <c r="D13" s="39" t="n">
+      <c r="D13" s="41" t="n">
         <v>2531</v>
       </c>
-      <c r="E13" s="39" t="n">
+      <c r="E13" s="41" t="n">
         <v>1809</v>
       </c>
       <c r="L13" s="9" t="inlineStr">
@@ -4817,15 +4722,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="38" t="inlineStr">
         <is>
           <t>Active communities</t>
         </is>
       </c>
-      <c r="D14" s="39" t="n">
+      <c r="D14" s="41" t="n">
         <v>220</v>
       </c>
-      <c r="E14" s="39" t="n">
+      <c r="E14" s="41" t="n">
         <v>232</v>
       </c>
     </row>
@@ -4846,18 +4751,18 @@
       <c r="J16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="36" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>Northern homebuilding</t>
         </is>
       </c>
-      <c r="C17" s="39" t="n">
+      <c r="C17" s="41" t="n">
         <v>1523943</v>
       </c>
-      <c r="D17" s="39" t="n">
+      <c r="D17" s="41" t="n">
         <v>1900013</v>
       </c>
-      <c r="E17" s="39" t="n">
+      <c r="E17" s="41" t="n">
         <v>1890457</v>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -4867,52 +4772,52 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="36" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>Southern homebuilding</t>
         </is>
       </c>
-      <c r="C18" s="39" t="n">
+      <c r="C18" s="41" t="n">
         <v>2415730</v>
       </c>
-      <c r="D18" s="39" t="n">
+      <c r="D18" s="41" t="n">
         <v>2488451</v>
       </c>
-      <c r="E18" s="39" t="n">
+      <c r="E18" s="41" t="n">
         <v>2401861</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="36" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>Financial services</t>
         </is>
       </c>
-      <c r="C19" s="39" t="n">
+      <c r="C19" s="41" t="n">
         <v>93829</v>
       </c>
-      <c r="D19" s="39" t="n">
+      <c r="D19" s="41" t="n">
         <v>116206</v>
       </c>
-      <c r="E19" s="39" t="n">
+      <c r="E19" s="41" t="n">
         <v>125463</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="42" t="inlineStr">
+      <c r="B20" s="44" t="inlineStr">
         <is>
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="45">
         <f>SUM(C17:C19)</f>
         <v/>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="45">
         <f>SUM(D17:D19)</f>
         <v/>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="45">
         <f>SUM(E17:E19)</f>
         <v/>
       </c>
@@ -4939,50 +4844,50 @@
       <c r="J22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="36" t="inlineStr">
+      <c r="B23" s="38" t="inlineStr">
         <is>
           <t>Northern</t>
         </is>
       </c>
-      <c r="C23" s="39" t="n">
+      <c r="C23" s="41" t="n">
         <v>1228949</v>
       </c>
-      <c r="D23" s="39" t="n">
+      <c r="D23" s="41" t="n">
         <v>1480326</v>
       </c>
-      <c r="E23" s="39" t="n">
+      <c r="E23" s="41" t="n">
         <v>1475438</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="36" t="inlineStr">
+      <c r="B24" s="38" t="inlineStr">
         <is>
           <t>Southern</t>
         </is>
       </c>
-      <c r="C24" s="39" t="n">
+      <c r="C24" s="41" t="n">
         <v>1785624</v>
       </c>
-      <c r="D24" s="39" t="n">
+      <c r="D24" s="41" t="n">
         <v>1825455</v>
       </c>
-      <c r="E24" s="39" t="n">
+      <c r="E24" s="41" t="n">
         <v>1925144</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="44" t="inlineStr">
+      <c r="B25" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  of which: inventory write-offs — Northern</t>
         </is>
       </c>
-      <c r="C25" s="39" t="n">
+      <c r="C25" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="39" t="n">
+      <c r="D25" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="39" t="n">
+      <c r="E25" s="41" t="n">
         <v>6700</v>
       </c>
       <c r="L25" s="9" t="inlineStr">
@@ -4992,18 +4897,18 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="44" t="inlineStr">
+      <c r="B26" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  of which: inventory write-offs — Southern</t>
         </is>
       </c>
-      <c r="C26" s="39" t="n">
+      <c r="C26" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="39" t="n">
+      <c r="D26" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="39" t="n">
+      <c r="E26" s="41" t="n">
         <v>41000</v>
       </c>
     </row>
@@ -5024,55 +4929,55 @@
       <c r="J28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="36" t="inlineStr">
+      <c r="B29" s="38" t="inlineStr">
         <is>
           <t>Northern homebuilding</t>
         </is>
       </c>
-      <c r="C29" s="39" t="n">
+      <c r="C29" s="41" t="n">
         <v>176320</v>
       </c>
-      <c r="D29" s="39" t="n">
+      <c r="D29" s="41" t="n">
         <v>281099</v>
       </c>
-      <c r="E29" s="39" t="n">
+      <c r="E29" s="41" t="n">
         <v>278056</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="36" t="inlineStr">
+      <c r="B30" s="38" t="inlineStr">
         <is>
           <t>Southern homebuilding</t>
         </is>
       </c>
-      <c r="C30" s="39" t="n">
+      <c r="C30" s="41" t="n">
         <v>440168</v>
       </c>
-      <c r="D30" s="39" t="n">
+      <c r="D30" s="41" t="n">
         <v>450598</v>
       </c>
-      <c r="E30" s="39" t="n">
+      <c r="E30" s="41" t="n">
         <v>249969</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="36" t="inlineStr">
+      <c r="B31" s="38" t="inlineStr">
         <is>
           <t>Financial services</t>
         </is>
       </c>
-      <c r="C31" s="39" t="n">
+      <c r="C31" s="41" t="n">
         <v>48714</v>
       </c>
-      <c r="D31" s="39" t="n">
+      <c r="D31" s="41" t="n">
         <v>63380</v>
       </c>
-      <c r="E31" s="39" t="n">
+      <c r="E31" s="41" t="n">
         <v>68160</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="36" t="inlineStr">
+      <c r="B32" s="38" t="inlineStr">
         <is>
           <t>Corporate / unallocated</t>
         </is>
@@ -5091,18 +4996,18 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="42" t="inlineStr">
+      <c r="B33" s="44" t="inlineStr">
         <is>
           <t>Total operating income</t>
         </is>
       </c>
-      <c r="C33" s="45" t="n">
+      <c r="C33" s="47" t="n">
         <v>587222</v>
       </c>
-      <c r="D33" s="45" t="n">
+      <c r="D33" s="47" t="n">
         <v>706094</v>
       </c>
-      <c r="E33" s="45" t="n">
+      <c r="E33" s="47" t="n">
         <v>506553</v>
       </c>
     </row>
@@ -5123,82 +5028,82 @@
       <c r="J35" s="3" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="36" t="inlineStr">
+      <c r="B36" s="38" t="inlineStr">
         <is>
           <t>Selling — Northern</t>
         </is>
       </c>
-      <c r="C36" s="39" t="n">
+      <c r="C36" s="41" t="n">
         <v>81847</v>
       </c>
-      <c r="D36" s="39" t="n">
+      <c r="D36" s="41" t="n">
         <v>95680</v>
       </c>
-      <c r="E36" s="39" t="n">
+      <c r="E36" s="41" t="n">
         <v>95860</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="36" t="inlineStr">
+      <c r="B37" s="38" t="inlineStr">
         <is>
           <t>Selling — Southern</t>
         </is>
       </c>
-      <c r="C37" s="39" t="n">
+      <c r="C37" s="41" t="n">
         <v>124860</v>
       </c>
-      <c r="D37" s="39" t="n">
+      <c r="D37" s="41" t="n">
         <v>136198</v>
       </c>
-      <c r="E37" s="39" t="n">
+      <c r="E37" s="41" t="n">
         <v>149457</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="36" t="inlineStr">
+      <c r="B38" s="38" t="inlineStr">
         <is>
           <t>G&amp;A — Northern</t>
         </is>
       </c>
-      <c r="C38" s="39" t="n">
+      <c r="C38" s="41" t="n">
         <v>36827</v>
       </c>
-      <c r="D38" s="39" t="n">
+      <c r="D38" s="41" t="n">
         <v>42908</v>
       </c>
-      <c r="E38" s="39" t="n">
+      <c r="E38" s="41" t="n">
         <v>41103</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="36" t="inlineStr">
+      <c r="B39" s="38" t="inlineStr">
         <is>
           <t>G&amp;A — Southern</t>
         </is>
       </c>
-      <c r="C39" s="39" t="n">
+      <c r="C39" s="41" t="n">
         <v>65078</v>
       </c>
-      <c r="D39" s="39" t="n">
+      <c r="D39" s="41" t="n">
         <v>76200</v>
       </c>
-      <c r="E39" s="39" t="n">
+      <c r="E39" s="41" t="n">
         <v>77291</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="36" t="inlineStr">
+      <c r="B40" s="38" t="inlineStr">
         <is>
           <t>G&amp;A — Financial services</t>
         </is>
       </c>
-      <c r="C40" s="39" t="n">
+      <c r="C40" s="41" t="n">
         <v>45115</v>
       </c>
-      <c r="D40" s="39" t="n">
+      <c r="D40" s="41" t="n">
         <v>52826</v>
       </c>
-      <c r="E40" s="39" t="n">
+      <c r="E40" s="41" t="n">
         <v>57303</v>
       </c>
     </row>
@@ -5219,114 +5124,114 @@
       <c r="J42" s="3" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="36" t="inlineStr">
+      <c r="B43" s="38" t="inlineStr">
         <is>
           <t>Land and housing costs</t>
         </is>
       </c>
-      <c r="C43" s="39" t="n">
+      <c r="C43" s="41" t="n">
         <v>3014573</v>
       </c>
-      <c r="D43" s="39" t="n">
+      <c r="D43" s="41" t="n">
         <v>3305781</v>
       </c>
-      <c r="E43" s="39" t="n">
+      <c r="E43" s="41" t="n">
         <v>3400582</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="36" t="inlineStr">
+      <c r="B44" s="38" t="inlineStr">
         <is>
           <t>Income before income taxes</t>
         </is>
       </c>
-      <c r="C44" s="39" t="n">
+      <c r="C44" s="41" t="n">
         <v>607277</v>
       </c>
-      <c r="D44" s="39" t="n">
+      <c r="D44" s="41" t="n">
         <v>733608</v>
       </c>
-      <c r="E44" s="39" t="n">
+      <c r="E44" s="41" t="n">
         <v>526588</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="36" t="inlineStr">
+      <c r="B45" s="38" t="inlineStr">
         <is>
           <t>Provision for income taxes</t>
         </is>
       </c>
-      <c r="C45" s="39" t="n">
+      <c r="C45" s="41" t="n">
         <v>141912</v>
       </c>
-      <c r="D45" s="39" t="n">
+      <c r="D45" s="41" t="n">
         <v>169883</v>
       </c>
-      <c r="E45" s="39" t="n">
+      <c r="E45" s="41" t="n">
         <v>123647</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="36" t="inlineStr">
+      <c r="B46" s="38" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="C46" s="39" t="n">
+      <c r="C46" s="41" t="n">
         <v>465365</v>
       </c>
-      <c r="D46" s="39" t="n">
+      <c r="D46" s="41" t="n">
         <v>563725</v>
       </c>
-      <c r="E46" s="39" t="n">
+      <c r="E46" s="41" t="n">
         <v>402941</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="36" t="inlineStr">
+      <c r="B47" s="38" t="inlineStr">
         <is>
           <t>Diluted EPS ($)</t>
         </is>
       </c>
-      <c r="C47" s="38" t="n">
+      <c r="C47" s="40" t="n">
         <v>16.21</v>
       </c>
-      <c r="D47" s="38" t="n">
+      <c r="D47" s="40" t="n">
         <v>19.71</v>
       </c>
-      <c r="E47" s="38" t="n">
+      <c r="E47" s="40" t="n">
         <v>14.74</v>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="36" t="inlineStr">
+      <c r="B48" s="38" t="inlineStr">
         <is>
           <t>Diluted weighted-average shares (000)</t>
         </is>
       </c>
-      <c r="C48" s="39" t="n">
+      <c r="C48" s="41" t="n">
         <v>28716</v>
       </c>
-      <c r="D48" s="39" t="n">
+      <c r="D48" s="41" t="n">
         <v>28600</v>
       </c>
-      <c r="E48" s="39" t="n">
+      <c r="E48" s="41" t="n">
         <v>27338</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="36" t="inlineStr">
+      <c r="B49" s="38" t="inlineStr">
         <is>
           <t>Shares outstanding, year end (000)</t>
         </is>
       </c>
-      <c r="C49" s="39" t="n">
+      <c r="C49" s="41" t="n">
         <v>27600</v>
       </c>
-      <c r="D49" s="39" t="n">
+      <c r="D49" s="41" t="n">
         <v>27060</v>
       </c>
-      <c r="E49" s="39" t="n">
+      <c r="E49" s="41" t="n">
         <v>25763</v>
       </c>
     </row>
@@ -5347,178 +5252,178 @@
       <c r="J51" s="3" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="36" t="inlineStr">
+      <c r="B52" s="38" t="inlineStr">
         <is>
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="C52" s="39" t="n">
+      <c r="C52" s="41" t="n">
         <v>733000</v>
       </c>
-      <c r="D52" s="39" t="n">
+      <c r="D52" s="41" t="n">
         <v>821600</v>
       </c>
-      <c r="E52" s="39" t="n">
+      <c r="E52" s="41" t="n">
         <v>689200</v>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="36" t="inlineStr">
+      <c r="B53" s="38" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C53" s="39" t="n">
+      <c r="C53" s="41" t="n">
         <v>2797151</v>
       </c>
-      <c r="D53" s="39" t="n">
+      <c r="D53" s="41" t="n">
         <v>3091862</v>
       </c>
-      <c r="E53" s="39" t="n">
+      <c r="E53" s="41" t="n">
         <v>3383941</v>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="36" t="inlineStr">
+      <c r="B54" s="38" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="C54" s="39" t="n">
+      <c r="C54" s="41" t="n">
         <v>4022440</v>
       </c>
-      <c r="D54" s="39" t="n">
+      <c r="D54" s="41" t="n">
         <v>4549796</v>
       </c>
-      <c r="E54" s="39" t="n">
+      <c r="E54" s="41" t="n">
         <v>4777125</v>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="36" t="inlineStr">
+      <c r="B55" s="38" t="inlineStr">
         <is>
           <t>Homebuilding debt</t>
         </is>
       </c>
-      <c r="C55" s="39" t="n">
+      <c r="C55" s="41" t="n">
         <v>693744</v>
       </c>
-      <c r="D55" s="39" t="n">
+      <c r="D55" s="41" t="n">
         <v>695022</v>
       </c>
-      <c r="E55" s="39" t="n">
+      <c r="E55" s="41" t="n">
         <v>696300</v>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="36" t="inlineStr">
+      <c r="B56" s="38" t="inlineStr">
         <is>
           <t>Financial services debt</t>
         </is>
       </c>
-      <c r="C56" s="39" t="n">
+      <c r="C56" s="41" t="n">
         <v>165844</v>
       </c>
-      <c r="D56" s="39" t="n">
+      <c r="D56" s="41" t="n">
         <v>286159</v>
       </c>
-      <c r="E56" s="39" t="n">
+      <c r="E56" s="41" t="n">
         <v>276856</v>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="36" t="inlineStr">
+      <c r="B57" s="38" t="inlineStr">
         <is>
           <t>Shareholders' equity</t>
         </is>
       </c>
-      <c r="C57" s="39" t="n">
+      <c r="C57" s="41" t="n">
         <v>2516939</v>
       </c>
-      <c r="D57" s="39" t="n">
+      <c r="D57" s="41" t="n">
         <v>2939677</v>
       </c>
-      <c r="E57" s="39" t="n">
+      <c r="E57" s="41" t="n">
         <v>3166190</v>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="36" t="inlineStr">
+      <c r="B58" s="38" t="inlineStr">
         <is>
           <t>Cash from operating activities</t>
         </is>
       </c>
-      <c r="C58" s="39" t="n">
+      <c r="C58" s="41" t="n">
         <v>552131</v>
       </c>
-      <c r="D58" s="39" t="n">
+      <c r="D58" s="41" t="n">
         <v>179736</v>
       </c>
-      <c r="E58" s="39" t="n">
+      <c r="E58" s="41" t="n">
         <v>137349</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="36" t="inlineStr">
+      <c r="B59" s="38" t="inlineStr">
         <is>
           <t>Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="C59" s="39" t="n">
+      <c r="C59" s="41" t="n">
         <v>15791</v>
       </c>
-      <c r="D59" s="39" t="n">
+      <c r="D59" s="41" t="n">
         <v>17386</v>
       </c>
-      <c r="E59" s="39" t="n">
+      <c r="E59" s="41" t="n">
         <v>18898</v>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="36" t="inlineStr">
+      <c r="B60" s="38" t="inlineStr">
         <is>
           <t>Stock-based compensation</t>
         </is>
       </c>
-      <c r="C60" s="39" t="n">
+      <c r="C60" s="41" t="n">
         <v>11370</v>
       </c>
-      <c r="D60" s="39" t="n">
+      <c r="D60" s="41" t="n">
         <v>14564</v>
       </c>
-      <c r="E60" s="39" t="n">
+      <c r="E60" s="41" t="n">
         <v>16998</v>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="36" t="inlineStr">
+      <c r="B61" s="38" t="inlineStr">
         <is>
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="C61" s="39" t="n">
+      <c r="C61" s="41" t="n">
         <v>5769</v>
       </c>
-      <c r="D61" s="39" t="n">
+      <c r="D61" s="41" t="n">
         <v>8417</v>
       </c>
-      <c r="E61" s="39" t="n">
+      <c r="E61" s="41" t="n">
         <v>9609</v>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="36" t="inlineStr">
+      <c r="B62" s="38" t="inlineStr">
         <is>
           <t>Share repurchases</t>
         </is>
       </c>
-      <c r="C62" s="39" t="n">
+      <c r="C62" s="41" t="n">
         <v>65344</v>
       </c>
-      <c r="D62" s="39" t="n">
+      <c r="D62" s="41" t="n">
         <v>176953</v>
       </c>
-      <c r="E62" s="39" t="n">
+      <c r="E62" s="41" t="n">
         <v>202033</v>
       </c>
     </row>
@@ -5539,20 +5444,20 @@
       <c r="J64" s="3" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="36" t="inlineStr">
+      <c r="B65" s="38" t="inlineStr">
         <is>
           <t>Net ASP — Northern ($000)</t>
         </is>
       </c>
-      <c r="C65" s="46">
+      <c r="C65" s="48">
         <f>C17/C8</f>
         <v/>
       </c>
-      <c r="D65" s="46">
+      <c r="D65" s="48">
         <f>D17/D8</f>
         <v/>
       </c>
-      <c r="E65" s="46">
+      <c r="E65" s="48">
         <f>E17/E8</f>
         <v/>
       </c>
@@ -5563,20 +5468,20 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="36" t="inlineStr">
+      <c r="B66" s="38" t="inlineStr">
         <is>
           <t>Net ASP — Southern ($000)</t>
         </is>
       </c>
-      <c r="C66" s="46">
+      <c r="C66" s="48">
         <f>C18/C9</f>
         <v/>
       </c>
-      <c r="D66" s="46">
+      <c r="D66" s="48">
         <f>D18/D9</f>
         <v/>
       </c>
-      <c r="E66" s="46">
+      <c r="E66" s="48">
         <f>E18/E9</f>
         <v/>
       </c>
@@ -5587,39 +5492,39 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="36" t="inlineStr">
+      <c r="B67" s="38" t="inlineStr">
         <is>
           <t>Cost per home ex-charges — Northern ($000)</t>
         </is>
       </c>
-      <c r="C67" s="46">
+      <c r="C67" s="48">
         <f>(C23-C25)/C8</f>
         <v/>
       </c>
-      <c r="D67" s="46">
+      <c r="D67" s="48">
         <f>(D23-D25)/D8</f>
         <v/>
       </c>
-      <c r="E67" s="46">
+      <c r="E67" s="48">
         <f>(E23-E25)/E8</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="36" t="inlineStr">
+      <c r="B68" s="38" t="inlineStr">
         <is>
           <t>Cost per home ex-charges — Southern ($000)</t>
         </is>
       </c>
-      <c r="C68" s="46">
+      <c r="C68" s="48">
         <f>(C24-C26)/C9</f>
         <v/>
       </c>
-      <c r="D68" s="46">
+      <c r="D68" s="48">
         <f>(D24-D26)/D9</f>
         <v/>
       </c>
-      <c r="E68" s="46">
+      <c r="E68" s="48">
         <f>(E24-E26)/E9</f>
         <v/>
       </c>
@@ -5630,7 +5535,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="36" t="inlineStr">
+      <c r="B69" s="38" t="inlineStr">
         <is>
           <t>Gross margin — Northern (%)</t>
         </is>
@@ -5649,7 +5554,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="36" t="inlineStr">
+      <c r="B70" s="38" t="inlineStr">
         <is>
           <t>Gross margin — Southern (%)</t>
         </is>
@@ -5673,7 +5578,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="36" t="inlineStr">
+      <c r="B71" s="38" t="inlineStr">
         <is>
           <t>Gross margin — homebuilding only (%)</t>
         </is>
@@ -5692,20 +5597,20 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="47" t="inlineStr">
+      <c r="B72" s="49" t="inlineStr">
         <is>
           <t>Gross margin — as reported (%)</t>
         </is>
       </c>
-      <c r="C72" s="32">
+      <c r="C72" s="34">
         <f>1-C43/C20</f>
         <v/>
       </c>
-      <c r="D72" s="32">
+      <c r="D72" s="34">
         <f>1-D43/D20</f>
         <v/>
       </c>
-      <c r="E72" s="32">
+      <c r="E72" s="34">
         <f>1-E43/E20</f>
         <v/>
       </c>
@@ -5716,7 +5621,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="36" t="inlineStr">
+      <c r="B73" s="38" t="inlineStr">
         <is>
           <t>Operating margin — Northern (%)</t>
         </is>
@@ -5735,20 +5640,20 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="47" t="inlineStr">
+      <c r="B74" s="49" t="inlineStr">
         <is>
           <t>Operating margin — Southern (%)</t>
         </is>
       </c>
-      <c r="C74" s="32">
+      <c r="C74" s="34">
         <f>C30/C18</f>
         <v/>
       </c>
-      <c r="D74" s="32">
+      <c r="D74" s="34">
         <f>D30/D18</f>
         <v/>
       </c>
-      <c r="E74" s="32">
+      <c r="E74" s="34">
         <f>E30/E18</f>
         <v/>
       </c>
@@ -5759,7 +5664,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="36" t="inlineStr">
+      <c r="B75" s="38" t="inlineStr">
         <is>
           <t>Southern share of deliveries (%)</t>
         </is>
@@ -5778,20 +5683,20 @@
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="47" t="inlineStr">
+      <c r="B76" s="49" t="inlineStr">
         <is>
           <t>Southern share of segment operating income (%)</t>
         </is>
       </c>
-      <c r="C76" s="32">
+      <c r="C76" s="34">
         <f>C30/(C29+C30)</f>
         <v/>
       </c>
-      <c r="D76" s="32">
+      <c r="D76" s="34">
         <f>D30/(D29+D30)</f>
         <v/>
       </c>
-      <c r="E76" s="32">
+      <c r="E76" s="34">
         <f>E30/(E29+E30)</f>
         <v/>
       </c>
@@ -5802,7 +5707,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="36" t="inlineStr">
+      <c r="B77" s="38" t="inlineStr">
         <is>
           <t>Return on equity (%)</t>
         </is>
@@ -5826,20 +5731,20 @@
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="36" t="inlineStr">
+      <c r="B78" s="38" t="inlineStr">
         <is>
           <t>Book value per share ($)</t>
         </is>
       </c>
-      <c r="C78" s="48">
+      <c r="C78" s="50">
         <f>C57/C49</f>
         <v/>
       </c>
-      <c r="D78" s="48">
+      <c r="D78" s="50">
         <f>D57/D49</f>
         <v/>
       </c>
-      <c r="E78" s="48">
+      <c r="E78" s="50">
         <f>E57/E49</f>
         <v/>
       </c>
@@ -5888,47 +5793,47 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>($ in thousands unless noted)</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>2023A</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>2024A</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>2025A</t>
         </is>
       </c>
-      <c r="F5" s="35" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="G5" s="35" t="inlineStr">
+      <c r="G5" s="37" t="inlineStr">
         <is>
           <t>2027E</t>
         </is>
       </c>
-      <c r="H5" s="35" t="inlineStr">
+      <c r="H5" s="37" t="inlineStr">
         <is>
           <t>2028E</t>
         </is>
       </c>
-      <c r="I5" s="35" t="inlineStr">
+      <c r="I5" s="37" t="inlineStr">
         <is>
           <t>2029E</t>
         </is>
       </c>
-      <c r="J5" s="35" t="inlineStr">
+      <c r="J5" s="37" t="inlineStr">
         <is>
           <t>2030E</t>
         </is>
@@ -5951,20 +5856,20 @@
       <c r="J7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Homes delivered</t>
         </is>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="51">
         <f>Historicals!C8</f>
         <v/>
       </c>
-      <c r="D8" s="49">
+      <c r="D8" s="51">
         <f>Historicals!D8</f>
         <v/>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="51">
         <f>Historicals!E8</f>
         <v/>
       </c>
@@ -5990,79 +5895,79 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>Gross ASP — list price before incentives ($000)</t>
         </is>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="48">
         <f>C11/(1-C10/100)</f>
         <v/>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="48">
         <f>D11/(1-D10/100)</f>
         <v/>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="48">
         <f>E11/(1-E10/100)</f>
         <v/>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="48">
         <f>E9*(1+Assumptions!F22/100)</f>
         <v/>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="48">
         <f>F9*(1+Assumptions!G22/100)</f>
         <v/>
       </c>
-      <c r="H9" s="46">
+      <c r="H9" s="48">
         <f>G9*(1+Assumptions!H22/100)</f>
         <v/>
       </c>
-      <c r="I9" s="46">
+      <c r="I9" s="48">
         <f>H9*(1+Assumptions!I22/100)</f>
         <v/>
       </c>
-      <c r="J9" s="46">
+      <c r="J9" s="48">
         <f>I9*(1+Assumptions!J22/100)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>Incentive load (% of gross ASP)</t>
         </is>
       </c>
-      <c r="C10" s="50">
+      <c r="C10" s="52">
         <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!C8-Assumptions!$C$9)+Assumptions!C14</f>
         <v/>
       </c>
-      <c r="D10" s="50">
+      <c r="D10" s="52">
         <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!D8-Assumptions!$C$9)+Assumptions!D14</f>
         <v/>
       </c>
-      <c r="E10" s="50">
+      <c r="E10" s="52">
         <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!E8-Assumptions!$C$9)+Assumptions!E14</f>
         <v/>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="52">
         <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!F8-Assumptions!$C$9)+Assumptions!F14</f>
         <v/>
       </c>
-      <c r="G10" s="50">
+      <c r="G10" s="52">
         <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!G8-Assumptions!$C$9)+Assumptions!G14</f>
         <v/>
       </c>
-      <c r="H10" s="50">
+      <c r="H10" s="52">
         <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!H8-Assumptions!$C$9)+Assumptions!H14</f>
         <v/>
       </c>
-      <c r="I10" s="50">
+      <c r="I10" s="52">
         <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!I8-Assumptions!$C$9)+Assumptions!I14</f>
         <v/>
       </c>
-      <c r="J10" s="50">
+      <c r="J10" s="52">
         <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!J8-Assumptions!$C$9)+Assumptions!J14</f>
         <v/>
       </c>
@@ -6073,196 +5978,196 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="47" t="inlineStr">
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>Net ASP — realised ($000)</t>
         </is>
       </c>
-      <c r="C11" s="51">
+      <c r="C11" s="53">
         <f>Historicals!C17/C8</f>
         <v/>
       </c>
-      <c r="D11" s="51">
+      <c r="D11" s="53">
         <f>Historicals!D17/D8</f>
         <v/>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="53">
         <f>Historicals!E17/E8</f>
         <v/>
       </c>
-      <c r="F11" s="52">
+      <c r="F11" s="54">
         <f>F9*(1-F10/100)</f>
         <v/>
       </c>
-      <c r="G11" s="52">
+      <c r="G11" s="54">
         <f>G9*(1-G10/100)</f>
         <v/>
       </c>
-      <c r="H11" s="52">
+      <c r="H11" s="54">
         <f>H9*(1-H10/100)</f>
         <v/>
       </c>
-      <c r="I11" s="52">
+      <c r="I11" s="54">
         <f>I9*(1-I10/100)</f>
         <v/>
       </c>
-      <c r="J11" s="52">
+      <c r="J11" s="54">
         <f>J9*(1-J10/100)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>Cost per home, ex-charges ($000)</t>
         </is>
       </c>
-      <c r="C12" s="53">
+      <c r="C12" s="55">
         <f>(Historicals!C23-Historicals!C25)/C8</f>
         <v/>
       </c>
-      <c r="D12" s="53">
+      <c r="D12" s="55">
         <f>(Historicals!D23-Historicals!D25)/D8</f>
         <v/>
       </c>
-      <c r="E12" s="53">
+      <c r="E12" s="55">
         <f>(Historicals!E23-Historicals!E25)/E8</f>
         <v/>
       </c>
-      <c r="F12" s="46">
+      <c r="F12" s="48">
         <f>E12*(1+Assumptions!F24/100)</f>
         <v/>
       </c>
-      <c r="G12" s="46">
+      <c r="G12" s="48">
         <f>F12*(1+Assumptions!G24/100)</f>
         <v/>
       </c>
-      <c r="H12" s="46">
+      <c r="H12" s="48">
         <f>G12*(1+Assumptions!H24/100)</f>
         <v/>
       </c>
-      <c r="I12" s="46">
+      <c r="I12" s="48">
         <f>H12*(1+Assumptions!I24/100)</f>
         <v/>
       </c>
-      <c r="J12" s="46">
+      <c r="J12" s="48">
         <f>I12*(1+Assumptions!J24/100)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>Gross profit per home ($000)</t>
         </is>
       </c>
-      <c r="C13" s="46">
+      <c r="C13" s="48">
         <f>C11-C12</f>
         <v/>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="48">
         <f>D11-D12</f>
         <v/>
       </c>
-      <c r="E13" s="46">
+      <c r="E13" s="48">
         <f>E11-E12</f>
         <v/>
       </c>
-      <c r="F13" s="46">
+      <c r="F13" s="48">
         <f>F11-F12</f>
         <v/>
       </c>
-      <c r="G13" s="46">
+      <c r="G13" s="48">
         <f>G11-G12</f>
         <v/>
       </c>
-      <c r="H13" s="46">
+      <c r="H13" s="48">
         <f>H11-H12</f>
         <v/>
       </c>
-      <c r="I13" s="46">
+      <c r="I13" s="48">
         <f>I11-I12</f>
         <v/>
       </c>
-      <c r="J13" s="46">
+      <c r="J13" s="48">
         <f>J11-J12</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="47" t="inlineStr">
+      <c r="B14" s="49" t="inlineStr">
         <is>
           <t>Gross margin, ex-charges (%)</t>
         </is>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="34">
         <f>1-C12/C11</f>
         <v/>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="34">
         <f>1-D12/D11</f>
         <v/>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="34">
         <f>1-E12/E11</f>
         <v/>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="34">
         <f>1-F12/F11</f>
         <v/>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="34">
         <f>1-G12/G11</f>
         <v/>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="34">
         <f>1-H12/H11</f>
         <v/>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="34">
         <f>1-I12/I11</f>
         <v/>
       </c>
-      <c r="J14" s="32">
+      <c r="J14" s="34">
         <f>1-J12/J11</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="42" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>Housing revenue</t>
         </is>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="45">
         <f>C8*C11</f>
         <v/>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="45">
         <f>D8*D11</f>
         <v/>
       </c>
-      <c r="E15" s="43">
+      <c r="E15" s="45">
         <f>E8*E11</f>
         <v/>
       </c>
-      <c r="F15" s="43">
+      <c r="F15" s="45">
         <f>F8*F11</f>
         <v/>
       </c>
-      <c r="G15" s="43">
+      <c r="G15" s="45">
         <f>G8*G11</f>
         <v/>
       </c>
-      <c r="H15" s="43">
+      <c r="H15" s="45">
         <f>H8*H11</f>
         <v/>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="45">
         <f>I8*I11</f>
         <v/>
       </c>
-      <c r="J15" s="43">
+      <c r="J15" s="45">
         <f>J8*J11</f>
         <v/>
       </c>
@@ -6284,20 +6189,20 @@
       <c r="J17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="36" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>Homes delivered</t>
         </is>
       </c>
-      <c r="C18" s="49">
+      <c r="C18" s="51">
         <f>Historicals!C9</f>
         <v/>
       </c>
-      <c r="D18" s="49">
+      <c r="D18" s="51">
         <f>Historicals!D9</f>
         <v/>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="51">
         <f>Historicals!E9</f>
         <v/>
       </c>
@@ -6323,79 +6228,79 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="36" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>Gross ASP — list price before incentives ($000)</t>
         </is>
       </c>
-      <c r="C19" s="46">
+      <c r="C19" s="48">
         <f>C21/(1-C20/100)</f>
         <v/>
       </c>
-      <c r="D19" s="46">
+      <c r="D19" s="48">
         <f>D21/(1-D20/100)</f>
         <v/>
       </c>
-      <c r="E19" s="46">
+      <c r="E19" s="48">
         <f>E21/(1-E20/100)</f>
         <v/>
       </c>
-      <c r="F19" s="46">
+      <c r="F19" s="48">
         <f>E19*(1+Assumptions!F23/100)</f>
         <v/>
       </c>
-      <c r="G19" s="46">
+      <c r="G19" s="48">
         <f>F19*(1+Assumptions!G23/100)</f>
         <v/>
       </c>
-      <c r="H19" s="46">
+      <c r="H19" s="48">
         <f>G19*(1+Assumptions!H23/100)</f>
         <v/>
       </c>
-      <c r="I19" s="46">
+      <c r="I19" s="48">
         <f>H19*(1+Assumptions!I23/100)</f>
         <v/>
       </c>
-      <c r="J19" s="46">
+      <c r="J19" s="48">
         <f>I19*(1+Assumptions!J23/100)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="36" t="inlineStr">
+      <c r="B20" s="38" t="inlineStr">
         <is>
           <t>Incentive load (% of gross ASP)</t>
         </is>
       </c>
-      <c r="C20" s="50">
+      <c r="C20" s="52">
         <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!C8-Assumptions!$C$9)+Assumptions!C17</f>
         <v/>
       </c>
-      <c r="D20" s="50">
+      <c r="D20" s="52">
         <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!D8-Assumptions!$C$9)+Assumptions!D17</f>
         <v/>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="52">
         <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!E8-Assumptions!$C$9)+Assumptions!E17</f>
         <v/>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="52">
         <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!F8-Assumptions!$C$9)+Assumptions!F17</f>
         <v/>
       </c>
-      <c r="G20" s="50">
+      <c r="G20" s="52">
         <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!G8-Assumptions!$C$9)+Assumptions!G17</f>
         <v/>
       </c>
-      <c r="H20" s="50">
+      <c r="H20" s="52">
         <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!H8-Assumptions!$C$9)+Assumptions!H17</f>
         <v/>
       </c>
-      <c r="I20" s="50">
+      <c r="I20" s="52">
         <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!I8-Assumptions!$C$9)+Assumptions!I17</f>
         <v/>
       </c>
-      <c r="J20" s="50">
+      <c r="J20" s="52">
         <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!J8-Assumptions!$C$9)+Assumptions!J17</f>
         <v/>
       </c>
@@ -6406,196 +6311,196 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="47" t="inlineStr">
+      <c r="B21" s="49" t="inlineStr">
         <is>
           <t>Net ASP — realised ($000)</t>
         </is>
       </c>
-      <c r="C21" s="51">
+      <c r="C21" s="53">
         <f>Historicals!C18/C18</f>
         <v/>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="53">
         <f>Historicals!D18/D18</f>
         <v/>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="53">
         <f>Historicals!E18/E18</f>
         <v/>
       </c>
-      <c r="F21" s="52">
+      <c r="F21" s="54">
         <f>F19*(1-F20/100)</f>
         <v/>
       </c>
-      <c r="G21" s="52">
+      <c r="G21" s="54">
         <f>G19*(1-G20/100)</f>
         <v/>
       </c>
-      <c r="H21" s="52">
+      <c r="H21" s="54">
         <f>H19*(1-H20/100)</f>
         <v/>
       </c>
-      <c r="I21" s="52">
+      <c r="I21" s="54">
         <f>I19*(1-I20/100)</f>
         <v/>
       </c>
-      <c r="J21" s="52">
+      <c r="J21" s="54">
         <f>J19*(1-J20/100)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="38" t="inlineStr">
         <is>
           <t>Cost per home, ex-charges ($000)</t>
         </is>
       </c>
-      <c r="C22" s="53">
+      <c r="C22" s="55">
         <f>(Historicals!C24-Historicals!C26)/C18</f>
         <v/>
       </c>
-      <c r="D22" s="53">
+      <c r="D22" s="55">
         <f>(Historicals!D24-Historicals!D26)/D18</f>
         <v/>
       </c>
-      <c r="E22" s="53">
+      <c r="E22" s="55">
         <f>(Historicals!E24-Historicals!E26)/E18</f>
         <v/>
       </c>
-      <c r="F22" s="46">
+      <c r="F22" s="48">
         <f>E22*(1+Assumptions!F25/100)</f>
         <v/>
       </c>
-      <c r="G22" s="46">
+      <c r="G22" s="48">
         <f>F22*(1+Assumptions!G25/100)</f>
         <v/>
       </c>
-      <c r="H22" s="46">
+      <c r="H22" s="48">
         <f>G22*(1+Assumptions!H25/100)</f>
         <v/>
       </c>
-      <c r="I22" s="46">
+      <c r="I22" s="48">
         <f>H22*(1+Assumptions!I25/100)</f>
         <v/>
       </c>
-      <c r="J22" s="46">
+      <c r="J22" s="48">
         <f>I22*(1+Assumptions!J25/100)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="36" t="inlineStr">
+      <c r="B23" s="38" t="inlineStr">
         <is>
           <t>Gross profit per home ($000)</t>
         </is>
       </c>
-      <c r="C23" s="46">
+      <c r="C23" s="48">
         <f>C21-C22</f>
         <v/>
       </c>
-      <c r="D23" s="46">
+      <c r="D23" s="48">
         <f>D21-D22</f>
         <v/>
       </c>
-      <c r="E23" s="46">
+      <c r="E23" s="48">
         <f>E21-E22</f>
         <v/>
       </c>
-      <c r="F23" s="46">
+      <c r="F23" s="48">
         <f>F21-F22</f>
         <v/>
       </c>
-      <c r="G23" s="46">
+      <c r="G23" s="48">
         <f>G21-G22</f>
         <v/>
       </c>
-      <c r="H23" s="46">
+      <c r="H23" s="48">
         <f>H21-H22</f>
         <v/>
       </c>
-      <c r="I23" s="46">
+      <c r="I23" s="48">
         <f>I21-I22</f>
         <v/>
       </c>
-      <c r="J23" s="46">
+      <c r="J23" s="48">
         <f>J21-J22</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="47" t="inlineStr">
+      <c r="B24" s="49" t="inlineStr">
         <is>
           <t>Gross margin, ex-charges (%)</t>
         </is>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="34">
         <f>1-C22/C21</f>
         <v/>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="34">
         <f>1-D22/D21</f>
         <v/>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="34">
         <f>1-E22/E21</f>
         <v/>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="34">
         <f>1-F22/F21</f>
         <v/>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="34">
         <f>1-G22/G21</f>
         <v/>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="34">
         <f>1-H22/H21</f>
         <v/>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="34">
         <f>1-I22/I21</f>
         <v/>
       </c>
-      <c r="J24" s="32">
+      <c r="J24" s="34">
         <f>1-J22/J21</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="42" t="inlineStr">
+      <c r="B25" s="44" t="inlineStr">
         <is>
           <t>Housing revenue</t>
         </is>
       </c>
-      <c r="C25" s="43">
+      <c r="C25" s="45">
         <f>C18*C21</f>
         <v/>
       </c>
-      <c r="D25" s="43">
+      <c r="D25" s="45">
         <f>D18*D21</f>
         <v/>
       </c>
-      <c r="E25" s="43">
+      <c r="E25" s="45">
         <f>E18*E21</f>
         <v/>
       </c>
-      <c r="F25" s="43">
+      <c r="F25" s="45">
         <f>F18*F21</f>
         <v/>
       </c>
-      <c r="G25" s="43">
+      <c r="G25" s="45">
         <f>G18*G21</f>
         <v/>
       </c>
-      <c r="H25" s="43">
+      <c r="H25" s="45">
         <f>H18*H21</f>
         <v/>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="45">
         <f>I18*I21</f>
         <v/>
       </c>
-      <c r="J25" s="43">
+      <c r="J25" s="45">
         <f>J18*J21</f>
         <v/>
       </c>
@@ -6617,7 +6522,7 @@
       <c r="J27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="36" t="inlineStr">
+      <c r="B28" s="38" t="inlineStr">
         <is>
           <t>Land sale revenue</t>
         </is>
@@ -6634,29 +6539,29 @@
         <f>Historicals!E17+Historicals!E18-E15-E25</f>
         <v/>
       </c>
-      <c r="F28" s="49">
+      <c r="F28" s="51">
         <f>Assumptions!F28</f>
         <v/>
       </c>
-      <c r="G28" s="49">
+      <c r="G28" s="51">
         <f>Assumptions!G28</f>
         <v/>
       </c>
-      <c r="H28" s="49">
+      <c r="H28" s="51">
         <f>Assumptions!H28</f>
         <v/>
       </c>
-      <c r="I28" s="49">
+      <c r="I28" s="51">
         <f>Assumptions!I28</f>
         <v/>
       </c>
-      <c r="J28" s="49">
+      <c r="J28" s="51">
         <f>Assumptions!J28</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="36" t="inlineStr">
+      <c r="B29" s="38" t="inlineStr">
         <is>
           <t>Financial services revenue</t>
         </is>
@@ -6711,7 +6616,7 @@
       <c r="J31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="36" t="inlineStr">
+      <c r="B32" s="38" t="inlineStr">
         <is>
           <t>Northern segment revenue</t>
         </is>
@@ -6750,7 +6655,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="36" t="inlineStr">
+      <c r="B33" s="38" t="inlineStr">
         <is>
           <t>Southern segment revenue</t>
         </is>
@@ -6789,86 +6694,86 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="42" t="inlineStr">
+      <c r="B34" s="44" t="inlineStr">
         <is>
           <t>Total homebuilding revenue</t>
         </is>
       </c>
-      <c r="C34" s="43">
+      <c r="C34" s="45">
         <f>C32+C33</f>
         <v/>
       </c>
-      <c r="D34" s="43">
+      <c r="D34" s="45">
         <f>D32+D33</f>
         <v/>
       </c>
-      <c r="E34" s="43">
+      <c r="E34" s="45">
         <f>E32+E33</f>
         <v/>
       </c>
-      <c r="F34" s="43">
+      <c r="F34" s="45">
         <f>F32+F33</f>
         <v/>
       </c>
-      <c r="G34" s="43">
+      <c r="G34" s="45">
         <f>G32+G33</f>
         <v/>
       </c>
-      <c r="H34" s="43">
+      <c r="H34" s="45">
         <f>H32+H33</f>
         <v/>
       </c>
-      <c r="I34" s="43">
+      <c r="I34" s="45">
         <f>I32+I33</f>
         <v/>
       </c>
-      <c r="J34" s="43">
+      <c r="J34" s="45">
         <f>J32+J33</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="42" t="inlineStr">
+      <c r="B35" s="44" t="inlineStr">
         <is>
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="C35" s="43">
+      <c r="C35" s="45">
         <f>C34+C29</f>
         <v/>
       </c>
-      <c r="D35" s="43">
+      <c r="D35" s="45">
         <f>D34+D29</f>
         <v/>
       </c>
-      <c r="E35" s="43">
+      <c r="E35" s="45">
         <f>E34+E29</f>
         <v/>
       </c>
-      <c r="F35" s="43">
+      <c r="F35" s="45">
         <f>F34+F29</f>
         <v/>
       </c>
-      <c r="G35" s="43">
+      <c r="G35" s="45">
         <f>G34+G29</f>
         <v/>
       </c>
-      <c r="H35" s="43">
+      <c r="H35" s="45">
         <f>H34+H29</f>
         <v/>
       </c>
-      <c r="I35" s="43">
+      <c r="I35" s="45">
         <f>I34+I29</f>
         <v/>
       </c>
-      <c r="J35" s="43">
+      <c r="J35" s="45">
         <f>J34+J29</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="6" customHeight="1"/>
     <row r="37">
-      <c r="B37" s="36" t="inlineStr">
+      <c r="B37" s="38" t="inlineStr">
         <is>
           <t>Land and housing costs</t>
         </is>
@@ -6907,79 +6812,79 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="47" t="inlineStr">
+      <c r="B38" s="49" t="inlineStr">
         <is>
           <t>Gross margin — homebuilding (%)</t>
         </is>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="34">
         <f>1-C37/C34</f>
         <v/>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="34">
         <f>1-D37/D34</f>
         <v/>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="34">
         <f>1-E37/E34</f>
         <v/>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="34">
         <f>1-F37/F34</f>
         <v/>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="34">
         <f>1-G37/G34</f>
         <v/>
       </c>
-      <c r="H38" s="32">
+      <c r="H38" s="34">
         <f>1-H37/H34</f>
         <v/>
       </c>
-      <c r="I38" s="32">
+      <c r="I38" s="34">
         <f>1-I37/I34</f>
         <v/>
       </c>
-      <c r="J38" s="32">
+      <c r="J38" s="34">
         <f>1-J37/J34</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="47" t="inlineStr">
+      <c r="B39" s="49" t="inlineStr">
         <is>
           <t>Gross margin — as reported by MHO (%)</t>
         </is>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="34">
         <f>1-C37/C35</f>
         <v/>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="34">
         <f>1-D37/D35</f>
         <v/>
       </c>
-      <c r="E39" s="32">
+      <c r="E39" s="34">
         <f>1-E37/E35</f>
         <v/>
       </c>
-      <c r="F39" s="32">
+      <c r="F39" s="34">
         <f>1-F37/F35</f>
         <v/>
       </c>
-      <c r="G39" s="32">
+      <c r="G39" s="34">
         <f>1-G37/G35</f>
         <v/>
       </c>
-      <c r="H39" s="32">
+      <c r="H39" s="34">
         <f>1-H37/H35</f>
         <v/>
       </c>
-      <c r="I39" s="32">
+      <c r="I39" s="34">
         <f>1-I37/I35</f>
         <v/>
       </c>
-      <c r="J39" s="32">
+      <c r="J39" s="34">
         <f>1-J37/J35</f>
         <v/>
       </c>
@@ -7006,39 +6911,39 @@
       <c r="J41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="36" t="inlineStr">
+      <c r="B42" s="38" t="inlineStr">
         <is>
           <t>Total revenue vs 10-K</t>
         </is>
       </c>
-      <c r="C42" s="46">
+      <c r="C42" s="48">
         <f>C35-Historicals!C20</f>
         <v/>
       </c>
-      <c r="D42" s="46">
+      <c r="D42" s="48">
         <f>D35-Historicals!D20</f>
         <v/>
       </c>
-      <c r="E42" s="46">
+      <c r="E42" s="48">
         <f>E35-Historicals!E20</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="36" t="inlineStr">
+      <c r="B43" s="38" t="inlineStr">
         <is>
           <t>Deliveries vs press release</t>
         </is>
       </c>
-      <c r="C43" s="46">
+      <c r="C43" s="48">
         <f>C8+C18-Historicals!C10</f>
         <v/>
       </c>
-      <c r="D43" s="46">
+      <c r="D43" s="48">
         <f>D8+D18-Historicals!D10</f>
         <v/>
       </c>
-      <c r="E43" s="46">
+      <c r="E43" s="48">
         <f>E8+E18-Historicals!E10</f>
         <v/>
       </c>
@@ -7087,47 +6992,47 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>($ in thousands unless noted)</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>2023A</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>2024A</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>2025A</t>
         </is>
       </c>
-      <c r="F5" s="35" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="G5" s="35" t="inlineStr">
+      <c r="G5" s="37" t="inlineStr">
         <is>
           <t>2027E</t>
         </is>
       </c>
-      <c r="H5" s="35" t="inlineStr">
+      <c r="H5" s="37" t="inlineStr">
         <is>
           <t>2028E</t>
         </is>
       </c>
-      <c r="I5" s="35" t="inlineStr">
+      <c r="I5" s="37" t="inlineStr">
         <is>
           <t>2029E</t>
         </is>
       </c>
-      <c r="J5" s="35" t="inlineStr">
+      <c r="J5" s="37" t="inlineStr">
         <is>
           <t>2030E</t>
         </is>
@@ -7150,163 +7055,163 @@
       <c r="J7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Northern homebuilding</t>
         </is>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="51">
         <f>'Segment Build'!C32</f>
         <v/>
       </c>
-      <c r="D8" s="49">
+      <c r="D8" s="51">
         <f>'Segment Build'!D32</f>
         <v/>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="51">
         <f>'Segment Build'!E32</f>
         <v/>
       </c>
-      <c r="F8" s="49">
+      <c r="F8" s="51">
         <f>'Segment Build'!F32</f>
         <v/>
       </c>
-      <c r="G8" s="49">
+      <c r="G8" s="51">
         <f>'Segment Build'!G32</f>
         <v/>
       </c>
-      <c r="H8" s="49">
+      <c r="H8" s="51">
         <f>'Segment Build'!H32</f>
         <v/>
       </c>
-      <c r="I8" s="49">
+      <c r="I8" s="51">
         <f>'Segment Build'!I32</f>
         <v/>
       </c>
-      <c r="J8" s="49">
+      <c r="J8" s="51">
         <f>'Segment Build'!J32</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>Southern homebuilding</t>
         </is>
       </c>
-      <c r="C9" s="49">
+      <c r="C9" s="51">
         <f>'Segment Build'!C33</f>
         <v/>
       </c>
-      <c r="D9" s="49">
+      <c r="D9" s="51">
         <f>'Segment Build'!D33</f>
         <v/>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="51">
         <f>'Segment Build'!E33</f>
         <v/>
       </c>
-      <c r="F9" s="49">
+      <c r="F9" s="51">
         <f>'Segment Build'!F33</f>
         <v/>
       </c>
-      <c r="G9" s="49">
+      <c r="G9" s="51">
         <f>'Segment Build'!G33</f>
         <v/>
       </c>
-      <c r="H9" s="49">
+      <c r="H9" s="51">
         <f>'Segment Build'!H33</f>
         <v/>
       </c>
-      <c r="I9" s="49">
+      <c r="I9" s="51">
         <f>'Segment Build'!I33</f>
         <v/>
       </c>
-      <c r="J9" s="49">
+      <c r="J9" s="51">
         <f>'Segment Build'!J33</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>Financial services</t>
         </is>
       </c>
-      <c r="C10" s="49">
+      <c r="C10" s="51">
         <f>'Segment Build'!C29</f>
         <v/>
       </c>
-      <c r="D10" s="49">
+      <c r="D10" s="51">
         <f>'Segment Build'!D29</f>
         <v/>
       </c>
-      <c r="E10" s="49">
+      <c r="E10" s="51">
         <f>'Segment Build'!E29</f>
         <v/>
       </c>
-      <c r="F10" s="49">
+      <c r="F10" s="51">
         <f>'Segment Build'!F29</f>
         <v/>
       </c>
-      <c r="G10" s="49">
+      <c r="G10" s="51">
         <f>'Segment Build'!G29</f>
         <v/>
       </c>
-      <c r="H10" s="49">
+      <c r="H10" s="51">
         <f>'Segment Build'!H29</f>
         <v/>
       </c>
-      <c r="I10" s="49">
+      <c r="I10" s="51">
         <f>'Segment Build'!I29</f>
         <v/>
       </c>
-      <c r="J10" s="49">
+      <c r="J10" s="51">
         <f>'Segment Build'!J29</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="42" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="45">
         <f>SUM(C8:C10)</f>
         <v/>
       </c>
-      <c r="D11" s="43">
+      <c r="D11" s="45">
         <f>SUM(D8:D10)</f>
         <v/>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="45">
         <f>SUM(E8:E10)</f>
         <v/>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="45">
         <f>SUM(F8:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="43">
+      <c r="G11" s="45">
         <f>SUM(G8:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="43">
+      <c r="H11" s="45">
         <f>SUM(H8:H10)</f>
         <v/>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="45">
         <f>SUM(I8:I10)</f>
         <v/>
       </c>
-      <c r="J11" s="43">
+      <c r="J11" s="45">
         <f>SUM(J8:J10)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="44" t="inlineStr">
+      <c r="B12" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">   growth (%)</t>
         </is>
@@ -7342,157 +7247,157 @@
     </row>
     <row r="13" ht="6" customHeight="1"/>
     <row r="14">
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="38" t="inlineStr">
         <is>
           <t>Land and housing costs</t>
         </is>
       </c>
-      <c r="C14" s="49">
+      <c r="C14" s="51">
         <f>'Segment Build'!C37</f>
         <v/>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="51">
         <f>'Segment Build'!D37</f>
         <v/>
       </c>
-      <c r="E14" s="49">
+      <c r="E14" s="51">
         <f>'Segment Build'!E37</f>
         <v/>
       </c>
-      <c r="F14" s="49">
+      <c r="F14" s="51">
         <f>'Segment Build'!F37</f>
         <v/>
       </c>
-      <c r="G14" s="49">
+      <c r="G14" s="51">
         <f>'Segment Build'!G37</f>
         <v/>
       </c>
-      <c r="H14" s="49">
+      <c r="H14" s="51">
         <f>'Segment Build'!H37</f>
         <v/>
       </c>
-      <c r="I14" s="49">
+      <c r="I14" s="51">
         <f>'Segment Build'!I37</f>
         <v/>
       </c>
-      <c r="J14" s="49">
+      <c r="J14" s="51">
         <f>'Segment Build'!J37</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="42" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="45">
         <f>C11-C14</f>
         <v/>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="45">
         <f>D11-D14</f>
         <v/>
       </c>
-      <c r="E15" s="43">
+      <c r="E15" s="45">
         <f>E11-E14</f>
         <v/>
       </c>
-      <c r="F15" s="43">
+      <c r="F15" s="45">
         <f>F11-F14</f>
         <v/>
       </c>
-      <c r="G15" s="43">
+      <c r="G15" s="45">
         <f>G11-G14</f>
         <v/>
       </c>
-      <c r="H15" s="43">
+      <c r="H15" s="45">
         <f>H11-H14</f>
         <v/>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="45">
         <f>I11-I14</f>
         <v/>
       </c>
-      <c r="J15" s="43">
+      <c r="J15" s="45">
         <f>J11-J14</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="54" t="inlineStr">
+      <c r="B16" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">   gross margin — as reported (%)</t>
         </is>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="34">
         <f>C15/C11</f>
         <v/>
       </c>
-      <c r="D16" s="32">
+      <c r="D16" s="34">
         <f>D15/D11</f>
         <v/>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="34">
         <f>E15/E11</f>
         <v/>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="34">
         <f>F15/F11</f>
         <v/>
       </c>
-      <c r="G16" s="32">
+      <c r="G16" s="34">
         <f>G15/G11</f>
         <v/>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="34">
         <f>H15/H11</f>
         <v/>
       </c>
-      <c r="I16" s="32">
+      <c r="I16" s="34">
         <f>I15/I11</f>
         <v/>
       </c>
-      <c r="J16" s="32">
+      <c r="J16" s="34">
         <f>J15/J11</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="54" t="inlineStr">
+      <c r="B17" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">   gross margin — homebuilding only (%)</t>
         </is>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="34">
         <f>1-C14/(C8+C9)</f>
         <v/>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="34">
         <f>1-D14/(D8+D9)</f>
         <v/>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="34">
         <f>1-E14/(E8+E9)</f>
         <v/>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="34">
         <f>1-F14/(F8+F9)</f>
         <v/>
       </c>
-      <c r="G17" s="32">
+      <c r="G17" s="34">
         <f>1-G14/(G8+G9)</f>
         <v/>
       </c>
-      <c r="H17" s="32">
+      <c r="H17" s="34">
         <f>1-H14/(H8+H9)</f>
         <v/>
       </c>
-      <c r="I17" s="32">
+      <c r="I17" s="34">
         <f>1-I14/(I8+I9)</f>
         <v/>
       </c>
-      <c r="J17" s="32">
+      <c r="J17" s="34">
         <f>1-J14/(J8+J9)</f>
         <v/>
       </c>
@@ -7514,7 +7419,7 @@
       <c r="J19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="36" t="inlineStr">
+      <c r="B20" s="38" t="inlineStr">
         <is>
           <t>Selling</t>
         </is>
@@ -7553,7 +7458,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="36" t="inlineStr">
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t>General and administrative</t>
         </is>
@@ -7592,7 +7497,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="38" t="inlineStr">
         <is>
           <t>Corporate / unallocated</t>
         </is>
@@ -7631,46 +7536,46 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="42" t="inlineStr">
+      <c r="B23" s="44" t="inlineStr">
         <is>
           <t>Total operating expenses</t>
         </is>
       </c>
-      <c r="C23" s="43">
+      <c r="C23" s="45">
         <f>SUM(C20:C22)</f>
         <v/>
       </c>
-      <c r="D23" s="43">
+      <c r="D23" s="45">
         <f>SUM(D20:D22)</f>
         <v/>
       </c>
-      <c r="E23" s="43">
+      <c r="E23" s="45">
         <f>SUM(E20:E22)</f>
         <v/>
       </c>
-      <c r="F23" s="43">
+      <c r="F23" s="45">
         <f>SUM(F20:F22)</f>
         <v/>
       </c>
-      <c r="G23" s="43">
+      <c r="G23" s="45">
         <f>SUM(G20:G22)</f>
         <v/>
       </c>
-      <c r="H23" s="43">
+      <c r="H23" s="45">
         <f>SUM(H20:H22)</f>
         <v/>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="45">
         <f>SUM(I20:I22)</f>
         <v/>
       </c>
-      <c r="J23" s="43">
+      <c r="J23" s="45">
         <f>SUM(J20:J22)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="44" t="inlineStr">
+      <c r="B24" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">   SG&amp;A as % of total revenue</t>
         </is>
@@ -7710,85 +7615,85 @@
     </row>
     <row r="25" ht="6" customHeight="1"/>
     <row r="26">
-      <c r="B26" s="42" t="inlineStr">
+      <c r="B26" s="44" t="inlineStr">
         <is>
           <t>OPERATING INCOME</t>
         </is>
       </c>
-      <c r="C26" s="43">
+      <c r="C26" s="45">
         <f>C15-C23</f>
         <v/>
       </c>
-      <c r="D26" s="43">
+      <c r="D26" s="45">
         <f>D15-D23</f>
         <v/>
       </c>
-      <c r="E26" s="43">
+      <c r="E26" s="45">
         <f>E15-E23</f>
         <v/>
       </c>
-      <c r="F26" s="43">
+      <c r="F26" s="45">
         <f>F15-F23</f>
         <v/>
       </c>
-      <c r="G26" s="43">
+      <c r="G26" s="45">
         <f>G15-G23</f>
         <v/>
       </c>
-      <c r="H26" s="43">
+      <c r="H26" s="45">
         <f>H15-H23</f>
         <v/>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="45">
         <f>I15-I23</f>
         <v/>
       </c>
-      <c r="J26" s="43">
+      <c r="J26" s="45">
         <f>J15-J23</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="54" t="inlineStr">
+      <c r="B27" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">   operating margin (%)</t>
         </is>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="34">
         <f>C26/C11</f>
         <v/>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="34">
         <f>D26/D11</f>
         <v/>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="34">
         <f>E26/E11</f>
         <v/>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="34">
         <f>F26/F11</f>
         <v/>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="34">
         <f>G26/G11</f>
         <v/>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="34">
         <f>H26/H11</f>
         <v/>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="34">
         <f>I26/I11</f>
         <v/>
       </c>
-      <c r="J27" s="32">
+      <c r="J27" s="34">
         <f>J26/J11</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="36" t="inlineStr">
+      <c r="B28" s="38" t="inlineStr">
         <is>
           <t>Interest income, net of interest expense</t>
         </is>
@@ -7827,46 +7732,46 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="42" t="inlineStr">
+      <c r="B29" s="44" t="inlineStr">
         <is>
           <t>Income before income taxes</t>
         </is>
       </c>
-      <c r="C29" s="43">
+      <c r="C29" s="45">
         <f>C26+C28</f>
         <v/>
       </c>
-      <c r="D29" s="43">
+      <c r="D29" s="45">
         <f>D26+D28</f>
         <v/>
       </c>
-      <c r="E29" s="43">
+      <c r="E29" s="45">
         <f>E26+E28</f>
         <v/>
       </c>
-      <c r="F29" s="43">
+      <c r="F29" s="45">
         <f>F26+F28</f>
         <v/>
       </c>
-      <c r="G29" s="43">
+      <c r="G29" s="45">
         <f>G26+G28</f>
         <v/>
       </c>
-      <c r="H29" s="43">
+      <c r="H29" s="45">
         <f>H26+H28</f>
         <v/>
       </c>
-      <c r="I29" s="43">
+      <c r="I29" s="45">
         <f>I26+I28</f>
         <v/>
       </c>
-      <c r="J29" s="43">
+      <c r="J29" s="45">
         <f>J26+J28</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="36" t="inlineStr">
+      <c r="B30" s="38" t="inlineStr">
         <is>
           <t>Provision for income taxes</t>
         </is>
@@ -7905,7 +7810,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="44" t="inlineStr">
+      <c r="B31" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">   effective tax rate (%)</t>
         </is>
@@ -7944,46 +7849,46 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="42" t="inlineStr">
+      <c r="B32" s="44" t="inlineStr">
         <is>
           <t>NET INCOME</t>
         </is>
       </c>
-      <c r="C32" s="43">
+      <c r="C32" s="45">
         <f>C29-C30</f>
         <v/>
       </c>
-      <c r="D32" s="43">
+      <c r="D32" s="45">
         <f>D29-D30</f>
         <v/>
       </c>
-      <c r="E32" s="43">
+      <c r="E32" s="45">
         <f>E29-E30</f>
         <v/>
       </c>
-      <c r="F32" s="43">
+      <c r="F32" s="45">
         <f>F29-F30</f>
         <v/>
       </c>
-      <c r="G32" s="43">
+      <c r="G32" s="45">
         <f>G29-G30</f>
         <v/>
       </c>
-      <c r="H32" s="43">
+      <c r="H32" s="45">
         <f>H29-H30</f>
         <v/>
       </c>
-      <c r="I32" s="43">
+      <c r="I32" s="45">
         <f>I29-I30</f>
         <v/>
       </c>
-      <c r="J32" s="43">
+      <c r="J32" s="45">
         <f>J29-J30</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="44" t="inlineStr">
+      <c r="B33" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">   net margin (%)</t>
         </is>
@@ -8038,7 +7943,7 @@
       <c r="J35" s="3" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="36" t="inlineStr">
+      <c r="B36" s="38" t="inlineStr">
         <is>
           <t>Diluted weighted-average shares (000)</t>
         </is>
@@ -8077,46 +7982,46 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="42" t="inlineStr">
+      <c r="B37" s="44" t="inlineStr">
         <is>
           <t>Diluted EPS ($)</t>
         </is>
       </c>
-      <c r="C37" s="55">
+      <c r="C37" s="57">
         <f>C32/C36</f>
         <v/>
       </c>
-      <c r="D37" s="55">
+      <c r="D37" s="57">
         <f>D32/D36</f>
         <v/>
       </c>
-      <c r="E37" s="55">
+      <c r="E37" s="57">
         <f>E32/E36</f>
         <v/>
       </c>
-      <c r="F37" s="55">
+      <c r="F37" s="57">
         <f>F32/F36</f>
         <v/>
       </c>
-      <c r="G37" s="55">
+      <c r="G37" s="57">
         <f>G32/G36</f>
         <v/>
       </c>
-      <c r="H37" s="55">
+      <c r="H37" s="57">
         <f>H32/H36</f>
         <v/>
       </c>
-      <c r="I37" s="55">
+      <c r="I37" s="57">
         <f>I32/I36</f>
         <v/>
       </c>
-      <c r="J37" s="55">
+      <c r="J37" s="57">
         <f>J32/J36</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="44" t="inlineStr">
+      <c r="B38" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">   growth (%)</t>
         </is>
@@ -8167,7 +8072,7 @@
       <c r="J40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="36" t="inlineStr">
+      <c r="B41" s="38" t="inlineStr">
         <is>
           <t>Northern homebuilding</t>
         </is>
@@ -8206,7 +8111,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="36" t="inlineStr">
+      <c r="B42" s="38" t="inlineStr">
         <is>
           <t>Southern homebuilding</t>
         </is>
@@ -8245,7 +8150,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="36" t="inlineStr">
+      <c r="B43" s="38" t="inlineStr">
         <is>
           <t>Financial services</t>
         </is>
@@ -8284,7 +8189,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="36" t="inlineStr">
+      <c r="B44" s="38" t="inlineStr">
         <is>
           <t>Northern operating margin (%)</t>
         </is>
@@ -8323,7 +8228,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="36" t="inlineStr">
+      <c r="B45" s="38" t="inlineStr">
         <is>
           <t>Southern operating margin (%)</t>
         </is>
@@ -8410,47 +8315,47 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>($ in thousands unless noted)</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>2023A</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>2024A</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>2025A</t>
         </is>
       </c>
-      <c r="F5" s="35" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="G5" s="35" t="inlineStr">
+      <c r="G5" s="37" t="inlineStr">
         <is>
           <t>2027E</t>
         </is>
       </c>
-      <c r="H5" s="35" t="inlineStr">
+      <c r="H5" s="37" t="inlineStr">
         <is>
           <t>2028E</t>
         </is>
       </c>
-      <c r="I5" s="35" t="inlineStr">
+      <c r="I5" s="37" t="inlineStr">
         <is>
           <t>2029E</t>
         </is>
       </c>
-      <c r="J5" s="35" t="inlineStr">
+      <c r="J5" s="37" t="inlineStr">
         <is>
           <t>2030E</t>
         </is>
@@ -8473,46 +8378,46 @@
       <c r="J7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="51">
         <f>Historicals!C52</f>
         <v/>
       </c>
-      <c r="D8" s="49">
+      <c r="D8" s="51">
         <f>Historicals!D52</f>
         <v/>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="51">
         <f>Historicals!E52</f>
         <v/>
       </c>
-      <c r="F8" s="49">
+      <c r="F8" s="51">
         <f>CF!F27</f>
         <v/>
       </c>
-      <c r="G8" s="49">
+      <c r="G8" s="51">
         <f>CF!G27</f>
         <v/>
       </c>
-      <c r="H8" s="49">
+      <c r="H8" s="51">
         <f>CF!H27</f>
         <v/>
       </c>
-      <c r="I8" s="49">
+      <c r="I8" s="51">
         <f>CF!I27</f>
         <v/>
       </c>
-      <c r="J8" s="49">
+      <c r="J8" s="51">
         <f>CF!J27</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
@@ -8556,7 +8461,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>Property and equipment, net</t>
         </is>
@@ -8595,7 +8500,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>Other assets (mortgage loans held for sale, deferred tax, other)</t>
         </is>
@@ -8634,40 +8539,40 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="42" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="45">
         <f>SUM(C8:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="45">
         <f>SUM(D8:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="45">
         <f>SUM(E8:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="45">
         <f>SUM(F8:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="45">
         <f>SUM(G8:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="43">
+      <c r="H12" s="45">
         <f>SUM(H8:H11)</f>
         <v/>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="45">
         <f>SUM(I8:I11)</f>
         <v/>
       </c>
-      <c r="J12" s="43">
+      <c r="J12" s="45">
         <f>SUM(J8:J11)</f>
         <v/>
       </c>
@@ -8689,85 +8594,85 @@
       <c r="J14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>Homebuilding debt (senior notes)</t>
         </is>
       </c>
-      <c r="C15" s="49">
+      <c r="C15" s="51">
         <f>Historicals!C55</f>
         <v/>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="51">
         <f>Historicals!D55</f>
         <v/>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="51">
         <f>Historicals!E55</f>
         <v/>
       </c>
-      <c r="F15" s="49">
+      <c r="F15" s="51">
         <f>Assumptions!F50</f>
         <v/>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="51">
         <f>Assumptions!G50</f>
         <v/>
       </c>
-      <c r="H15" s="49">
+      <c r="H15" s="51">
         <f>Assumptions!H50</f>
         <v/>
       </c>
-      <c r="I15" s="49">
+      <c r="I15" s="51">
         <f>Assumptions!I50</f>
         <v/>
       </c>
-      <c r="J15" s="49">
+      <c r="J15" s="51">
         <f>Assumptions!J50</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="36" t="inlineStr">
+      <c r="B16" s="38" t="inlineStr">
         <is>
           <t>Financial services debt (warehouse facilities)</t>
         </is>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="51">
         <f>Historicals!C56</f>
         <v/>
       </c>
-      <c r="D16" s="49">
+      <c r="D16" s="51">
         <f>Historicals!D56</f>
         <v/>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="51">
         <f>Historicals!E56</f>
         <v/>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="51">
         <f>Assumptions!F51</f>
         <v/>
       </c>
-      <c r="G16" s="49">
+      <c r="G16" s="51">
         <f>Assumptions!G51</f>
         <v/>
       </c>
-      <c r="H16" s="49">
+      <c r="H16" s="51">
         <f>Assumptions!H51</f>
         <v/>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="51">
         <f>Assumptions!I51</f>
         <v/>
       </c>
-      <c r="J16" s="49">
+      <c r="J16" s="51">
         <f>Assumptions!J51</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="36" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>Accounts payable, accruals, deposits and other</t>
         </is>
@@ -8806,157 +8711,157 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="45">
         <f>SUM(C15:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="43">
+      <c r="D18" s="45">
         <f>SUM(D15:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="45">
         <f>SUM(E15:E17)</f>
         <v/>
       </c>
-      <c r="F18" s="43">
+      <c r="F18" s="45">
         <f>SUM(F15:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="43">
+      <c r="G18" s="45">
         <f>SUM(G15:G17)</f>
         <v/>
       </c>
-      <c r="H18" s="43">
+      <c r="H18" s="45">
         <f>SUM(H15:H17)</f>
         <v/>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="45">
         <f>SUM(I15:I17)</f>
         <v/>
       </c>
-      <c r="J18" s="43">
+      <c r="J18" s="45">
         <f>SUM(J15:J17)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="47" t="inlineStr">
+      <c r="B19" s="49" t="inlineStr">
         <is>
           <t>Shareholders' equity</t>
         </is>
       </c>
-      <c r="C19" s="56">
+      <c r="C19" s="58">
         <f>Historicals!C57</f>
         <v/>
       </c>
-      <c r="D19" s="56">
+      <c r="D19" s="58">
         <f>Historicals!D57</f>
         <v/>
       </c>
-      <c r="E19" s="56">
+      <c r="E19" s="58">
         <f>Historicals!E57</f>
         <v/>
       </c>
-      <c r="F19" s="56">
+      <c r="F19" s="58">
         <f>E19+IS!F32+Assumptions!F46-Assumptions!F47</f>
         <v/>
       </c>
-      <c r="G19" s="56">
+      <c r="G19" s="58">
         <f>F19+IS!G32+Assumptions!G46-Assumptions!G47</f>
         <v/>
       </c>
-      <c r="H19" s="56">
+      <c r="H19" s="58">
         <f>G19+IS!H32+Assumptions!H46-Assumptions!H47</f>
         <v/>
       </c>
-      <c r="I19" s="56">
+      <c r="I19" s="58">
         <f>H19+IS!I32+Assumptions!I46-Assumptions!I47</f>
         <v/>
       </c>
-      <c r="J19" s="56">
+      <c r="J19" s="58">
         <f>I19+IS!J32+Assumptions!J46-Assumptions!J47</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="42" t="inlineStr">
+      <c r="B20" s="44" t="inlineStr">
         <is>
           <t>TOTAL LIABILITIES AND EQUITY</t>
         </is>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="45">
         <f>C18+C19</f>
         <v/>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="45">
         <f>D18+D19</f>
         <v/>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="45">
         <f>E18+E19</f>
         <v/>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="45">
         <f>F18+F19</f>
         <v/>
       </c>
-      <c r="G20" s="43">
+      <c r="G20" s="45">
         <f>G18+G19</f>
         <v/>
       </c>
-      <c r="H20" s="43">
+      <c r="H20" s="45">
         <f>H18+H19</f>
         <v/>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="45">
         <f>I18+I19</f>
         <v/>
       </c>
-      <c r="J20" s="43">
+      <c r="J20" s="45">
         <f>J18+J19</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="47" t="inlineStr">
+      <c r="B21" s="49" t="inlineStr">
         <is>
           <t>CHECK — assets less liabilities and equity</t>
         </is>
       </c>
-      <c r="C21" s="57">
+      <c r="C21" s="59">
         <f>C12-C20</f>
         <v/>
       </c>
-      <c r="D21" s="57">
+      <c r="D21" s="59">
         <f>D12-D20</f>
         <v/>
       </c>
-      <c r="E21" s="57">
+      <c r="E21" s="59">
         <f>E12-E20</f>
         <v/>
       </c>
-      <c r="F21" s="57">
+      <c r="F21" s="59">
         <f>F12-F20</f>
         <v/>
       </c>
-      <c r="G21" s="57">
+      <c r="G21" s="59">
         <f>G12-G20</f>
         <v/>
       </c>
-      <c r="H21" s="57">
+      <c r="H21" s="59">
         <f>H12-H20</f>
         <v/>
       </c>
-      <c r="I21" s="57">
+      <c r="I21" s="59">
         <f>I12-I20</f>
         <v/>
       </c>
-      <c r="J21" s="57">
+      <c r="J21" s="59">
         <f>J12-J20</f>
         <v/>
       </c>
@@ -8983,7 +8888,7 @@
       <c r="J23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="36" t="inlineStr">
+      <c r="B24" s="38" t="inlineStr">
         <is>
           <t>Shares outstanding, year end (000)</t>
         </is>
@@ -9022,79 +8927,79 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="42" t="inlineStr">
+      <c r="B25" s="44" t="inlineStr">
         <is>
           <t>Book value per share ($)</t>
         </is>
       </c>
-      <c r="C25" s="55">
+      <c r="C25" s="57">
         <f>C19/C24</f>
         <v/>
       </c>
-      <c r="D25" s="55">
+      <c r="D25" s="57">
         <f>D19/D24</f>
         <v/>
       </c>
-      <c r="E25" s="55">
+      <c r="E25" s="57">
         <f>E19/E24</f>
         <v/>
       </c>
-      <c r="F25" s="55">
+      <c r="F25" s="57">
         <f>F19/F24</f>
         <v/>
       </c>
-      <c r="G25" s="55">
+      <c r="G25" s="57">
         <f>G19/G24</f>
         <v/>
       </c>
-      <c r="H25" s="55">
+      <c r="H25" s="57">
         <f>H19/H24</f>
         <v/>
       </c>
-      <c r="I25" s="55">
+      <c r="I25" s="57">
         <f>I19/I24</f>
         <v/>
       </c>
-      <c r="J25" s="55">
+      <c r="J25" s="57">
         <f>J19/J24</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="36" t="inlineStr">
+      <c r="B26" s="38" t="inlineStr">
         <is>
           <t>Tangible book value per share ($)</t>
         </is>
       </c>
-      <c r="C26" s="48">
+      <c r="C26" s="50">
         <f>(C19-16100)/C24</f>
         <v/>
       </c>
-      <c r="D26" s="48">
+      <c r="D26" s="50">
         <f>(D19-16100)/D24</f>
         <v/>
       </c>
-      <c r="E26" s="48">
+      <c r="E26" s="50">
         <f>(E19-16100)/E24</f>
         <v/>
       </c>
-      <c r="F26" s="48">
+      <c r="F26" s="50">
         <f>(F19-16100)/F24</f>
         <v/>
       </c>
-      <c r="G26" s="48">
+      <c r="G26" s="50">
         <f>(G19-16100)/G24</f>
         <v/>
       </c>
-      <c r="H26" s="48">
+      <c r="H26" s="50">
         <f>(H19-16100)/H24</f>
         <v/>
       </c>
-      <c r="I26" s="48">
+      <c r="I26" s="50">
         <f>(I19-16100)/I24</f>
         <v/>
       </c>
-      <c r="J26" s="48">
+      <c r="J26" s="50">
         <f>(J19-16100)/J24</f>
         <v/>
       </c>
@@ -9105,7 +9010,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="36" t="inlineStr">
+      <c r="B27" s="38" t="inlineStr">
         <is>
           <t>Net debt / (net cash) — homebuilding only</t>
         </is>
@@ -9149,7 +9054,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="36" t="inlineStr">
+      <c r="B28" s="38" t="inlineStr">
         <is>
           <t>Homebuilding debt / total capital (%)</t>
         </is>
@@ -9188,40 +9093,40 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="47" t="inlineStr">
+      <c r="B29" s="49" t="inlineStr">
         <is>
           <t>Return on equity (%)</t>
         </is>
       </c>
-      <c r="C29" s="32">
+      <c r="C29" s="34">
         <f>IS!C32/C19</f>
         <v/>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="34">
         <f>IS!D32/D19</f>
         <v/>
       </c>
-      <c r="E29" s="32">
+      <c r="E29" s="34">
         <f>IS!E32/E19</f>
         <v/>
       </c>
-      <c r="F29" s="32">
+      <c r="F29" s="34">
         <f>IS!F32/F19</f>
         <v/>
       </c>
-      <c r="G29" s="32">
+      <c r="G29" s="34">
         <f>IS!G32/G19</f>
         <v/>
       </c>
-      <c r="H29" s="32">
+      <c r="H29" s="34">
         <f>IS!H32/H19</f>
         <v/>
       </c>
-      <c r="I29" s="32">
+      <c r="I29" s="34">
         <f>IS!I32/I19</f>
         <v/>
       </c>
-      <c r="J29" s="32">
+      <c r="J29" s="34">
         <f>IS!J32/J19</f>
         <v/>
       </c>
@@ -9232,40 +9137,40 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="36" t="inlineStr">
+      <c r="B30" s="38" t="inlineStr">
         <is>
           <t>Inventory turns (x)</t>
         </is>
       </c>
-      <c r="C30" s="58">
+      <c r="C30" s="60">
         <f>'Segment Build'!C34/C9</f>
         <v/>
       </c>
-      <c r="D30" s="58">
+      <c r="D30" s="60">
         <f>'Segment Build'!D34/D9</f>
         <v/>
       </c>
-      <c r="E30" s="58">
+      <c r="E30" s="60">
         <f>'Segment Build'!E34/E9</f>
         <v/>
       </c>
-      <c r="F30" s="58">
+      <c r="F30" s="60">
         <f>'Segment Build'!F34/F9</f>
         <v/>
       </c>
-      <c r="G30" s="58">
+      <c r="G30" s="60">
         <f>'Segment Build'!G34/G9</f>
         <v/>
       </c>
-      <c r="H30" s="58">
+      <c r="H30" s="60">
         <f>'Segment Build'!H34/H9</f>
         <v/>
       </c>
-      <c r="I30" s="58">
+      <c r="I30" s="60">
         <f>'Segment Build'!I34/I9</f>
         <v/>
       </c>
-      <c r="J30" s="58">
+      <c r="J30" s="60">
         <f>'Segment Build'!J34/J9</f>
         <v/>
       </c>
@@ -9314,47 +9219,47 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>($ in thousands unless noted)</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>2023A</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>2024A</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>2025A</t>
         </is>
       </c>
-      <c r="F5" s="35" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="G5" s="35" t="inlineStr">
+      <c r="G5" s="37" t="inlineStr">
         <is>
           <t>2027E</t>
         </is>
       </c>
-      <c r="H5" s="35" t="inlineStr">
+      <c r="H5" s="37" t="inlineStr">
         <is>
           <t>2028E</t>
         </is>
       </c>
-      <c r="I5" s="35" t="inlineStr">
+      <c r="I5" s="37" t="inlineStr">
         <is>
           <t>2029E</t>
         </is>
       </c>
-      <c r="J5" s="35" t="inlineStr">
+      <c r="J5" s="37" t="inlineStr">
         <is>
           <t>2030E</t>
         </is>
@@ -9377,46 +9282,46 @@
       <c r="J7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="51">
         <f>IS!C32</f>
         <v/>
       </c>
-      <c r="D8" s="49">
+      <c r="D8" s="51">
         <f>IS!D32</f>
         <v/>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="51">
         <f>IS!E32</f>
         <v/>
       </c>
-      <c r="F8" s="49">
+      <c r="F8" s="51">
         <f>IS!F32</f>
         <v/>
       </c>
-      <c r="G8" s="49">
+      <c r="G8" s="51">
         <f>IS!G32</f>
         <v/>
       </c>
-      <c r="H8" s="49">
+      <c r="H8" s="51">
         <f>IS!H32</f>
         <v/>
       </c>
-      <c r="I8" s="49">
+      <c r="I8" s="51">
         <f>IS!I32</f>
         <v/>
       </c>
-      <c r="J8" s="49">
+      <c r="J8" s="51">
         <f>IS!J32</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>Depreciation and amortisation</t>
         </is>
@@ -9455,7 +9360,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>Stock-based compensation</t>
         </is>
@@ -9494,7 +9399,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>(Increase) / decrease in inventory</t>
         </is>
@@ -9526,7 +9431,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>(Increase) / decrease in other operating assets</t>
         </is>
@@ -9553,7 +9458,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>Increase / (decrease) in other liabilities</t>
         </is>
@@ -9580,40 +9485,40 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="44" t="inlineStr">
         <is>
           <t>CASH FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
-      <c r="C14" s="43">
+      <c r="C14" s="45">
         <f>Historicals!C58</f>
         <v/>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="45">
         <f>Historicals!D58</f>
         <v/>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="45">
         <f>Historicals!E58</f>
         <v/>
       </c>
-      <c r="F14" s="43">
+      <c r="F14" s="45">
         <f>SUM(F8:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="43">
+      <c r="G14" s="45">
         <f>SUM(G8:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="43">
+      <c r="H14" s="45">
         <f>SUM(H8:H13)</f>
         <v/>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="45">
         <f>SUM(I8:I13)</f>
         <v/>
       </c>
-      <c r="J14" s="43">
+      <c r="J14" s="45">
         <f>SUM(J8:J13)</f>
         <v/>
       </c>
@@ -9635,7 +9540,7 @@
       <c r="J16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="36" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>Capital expenditure</t>
         </is>
@@ -9674,40 +9579,40 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>CASH FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="45">
         <f>C17</f>
         <v/>
       </c>
-      <c r="D18" s="43">
+      <c r="D18" s="45">
         <f>D17</f>
         <v/>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="45">
         <f>E17</f>
         <v/>
       </c>
-      <c r="F18" s="43">
+      <c r="F18" s="45">
         <f>F17</f>
         <v/>
       </c>
-      <c r="G18" s="43">
+      <c r="G18" s="45">
         <f>G17</f>
         <v/>
       </c>
-      <c r="H18" s="43">
+      <c r="H18" s="45">
         <f>H17</f>
         <v/>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="45">
         <f>I17</f>
         <v/>
       </c>
-      <c r="J18" s="43">
+      <c r="J18" s="45">
         <f>J17</f>
         <v/>
       </c>
@@ -9729,7 +9634,7 @@
       <c r="J20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="36" t="inlineStr">
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t>Net change in debt</t>
         </is>
@@ -9756,7 +9661,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="38" t="inlineStr">
         <is>
           <t>Share repurchases</t>
         </is>
@@ -9800,7 +9705,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="42" t="inlineStr">
+      <c r="B23" s="44" t="inlineStr">
         <is>
           <t>CASH FROM FINANCING ACTIVITIES</t>
         </is>
@@ -9808,30 +9713,30 @@
       <c r="C23" s="19" t="n"/>
       <c r="D23" s="19" t="n"/>
       <c r="E23" s="19" t="n"/>
-      <c r="F23" s="43">
+      <c r="F23" s="45">
         <f>F21+F22</f>
         <v/>
       </c>
-      <c r="G23" s="43">
+      <c r="G23" s="45">
         <f>G21+G22</f>
         <v/>
       </c>
-      <c r="H23" s="43">
+      <c r="H23" s="45">
         <f>H21+H22</f>
         <v/>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="45">
         <f>I21+I22</f>
         <v/>
       </c>
-      <c r="J23" s="43">
+      <c r="J23" s="45">
         <f>J21+J22</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="6" customHeight="1"/>
     <row r="25">
-      <c r="B25" s="42" t="inlineStr">
+      <c r="B25" s="44" t="inlineStr">
         <is>
           <t>Net change in cash</t>
         </is>
@@ -9839,29 +9744,29 @@
       <c r="C25" s="19" t="n"/>
       <c r="D25" s="19" t="n"/>
       <c r="E25" s="19" t="n"/>
-      <c r="F25" s="43">
+      <c r="F25" s="45">
         <f>F14+F18+F23</f>
         <v/>
       </c>
-      <c r="G25" s="43">
+      <c r="G25" s="45">
         <f>G14+G18+G23</f>
         <v/>
       </c>
-      <c r="H25" s="43">
+      <c r="H25" s="45">
         <f>H14+H18+H23</f>
         <v/>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="45">
         <f>I14+I18+I23</f>
         <v/>
       </c>
-      <c r="J25" s="43">
+      <c r="J25" s="45">
         <f>J14+J18+J23</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="36" t="inlineStr">
+      <c r="B26" s="38" t="inlineStr">
         <is>
           <t>Cash, beginning of period</t>
         </is>
@@ -9888,40 +9793,40 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="42" t="inlineStr">
+      <c r="B27" s="44" t="inlineStr">
         <is>
           <t>CASH, END OF PERIOD</t>
         </is>
       </c>
-      <c r="C27" s="43">
+      <c r="C27" s="45">
         <f>Historicals!C52</f>
         <v/>
       </c>
-      <c r="D27" s="43">
+      <c r="D27" s="45">
         <f>Historicals!D52</f>
         <v/>
       </c>
-      <c r="E27" s="43">
+      <c r="E27" s="45">
         <f>Historicals!E52</f>
         <v/>
       </c>
-      <c r="F27" s="43">
+      <c r="F27" s="45">
         <f>F26+F25</f>
         <v/>
       </c>
-      <c r="G27" s="43">
+      <c r="G27" s="45">
         <f>G26+G25</f>
         <v/>
       </c>
-      <c r="H27" s="43">
+      <c r="H27" s="45">
         <f>H26+H25</f>
         <v/>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="45">
         <f>I26+I25</f>
         <v/>
       </c>
-      <c r="J27" s="43">
+      <c r="J27" s="45">
         <f>J26+J25</f>
         <v/>
       </c>
@@ -9943,46 +9848,46 @@
       <c r="J29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="47" t="inlineStr">
+      <c r="B30" s="49" t="inlineStr">
         <is>
           <t>Operating cash flow less capex</t>
         </is>
       </c>
-      <c r="C30" s="56">
+      <c r="C30" s="58">
         <f>C14+C18</f>
         <v/>
       </c>
-      <c r="D30" s="56">
+      <c r="D30" s="58">
         <f>D14+D18</f>
         <v/>
       </c>
-      <c r="E30" s="56">
+      <c r="E30" s="58">
         <f>E14+E18</f>
         <v/>
       </c>
-      <c r="F30" s="56">
+      <c r="F30" s="58">
         <f>F14+F18</f>
         <v/>
       </c>
-      <c r="G30" s="56">
+      <c r="G30" s="58">
         <f>G14+G18</f>
         <v/>
       </c>
-      <c r="H30" s="56">
+      <c r="H30" s="58">
         <f>H14+H18</f>
         <v/>
       </c>
-      <c r="I30" s="56">
+      <c r="I30" s="58">
         <f>I14+I18</f>
         <v/>
       </c>
-      <c r="J30" s="56">
+      <c r="J30" s="58">
         <f>J14+J18</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="44" t="inlineStr">
+      <c r="B31" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">   as % of net income</t>
         </is>
@@ -10089,7 +9994,7 @@
           <t>Risk-free rate — 10-yr UST</t>
         </is>
       </c>
-      <c r="C6" s="50">
+      <c r="C6" s="52">
         <f>Assumptions!$C$55</f>
         <v/>
       </c>
@@ -10100,7 +10005,7 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="C7" s="50">
+      <c r="C7" s="52">
         <f>Assumptions!$C$56</f>
         <v/>
       </c>
@@ -10111,7 +10016,7 @@
           <t>Levered beta</t>
         </is>
       </c>
-      <c r="C8" s="48">
+      <c r="C8" s="50">
         <f>Assumptions!$C$57</f>
         <v/>
       </c>
@@ -10122,7 +10027,7 @@
           <t>Cost of equity</t>
         </is>
       </c>
-      <c r="C9" s="59">
+      <c r="C9" s="61">
         <f>C6+C8*C7</f>
         <v/>
       </c>
@@ -10133,7 +10038,7 @@
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="C10" s="50">
+      <c r="C10" s="52">
         <f>Assumptions!$C$58</f>
         <v/>
       </c>
@@ -10144,7 +10049,7 @@
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="C11" s="50">
+      <c r="C11" s="52">
         <f>C10*(1-Assumptions!$C$38/100)</f>
         <v/>
       </c>
@@ -10209,7 +10114,7 @@
           <t>WACC</t>
         </is>
       </c>
-      <c r="C16" s="59">
+      <c r="C16" s="61">
         <f>C14*C9+C15*C11</f>
         <v/>
       </c>
@@ -10220,7 +10125,7 @@
           <t>Terminal growth rate</t>
         </is>
       </c>
-      <c r="C17" s="50">
+      <c r="C17" s="52">
         <f>Assumptions!$C$59</f>
         <v/>
       </c>
@@ -10242,69 +10147,69 @@
       <c r="J19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>($ in thousands)</t>
         </is>
       </c>
-      <c r="C20" s="60" t="n"/>
-      <c r="D20" s="60" t="n"/>
-      <c r="E20" s="60" t="n"/>
-      <c r="F20" s="31" t="inlineStr">
+      <c r="C20" s="62" t="n"/>
+      <c r="D20" s="62" t="n"/>
+      <c r="E20" s="62" t="n"/>
+      <c r="F20" s="33" t="inlineStr">
         <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="G20" s="31" t="inlineStr">
+      <c r="G20" s="33" t="inlineStr">
         <is>
           <t>2027E</t>
         </is>
       </c>
-      <c r="H20" s="31" t="inlineStr">
+      <c r="H20" s="33" t="inlineStr">
         <is>
           <t>2028E</t>
         </is>
       </c>
-      <c r="I20" s="31" t="inlineStr">
+      <c r="I20" s="33" t="inlineStr">
         <is>
           <t>2029E</t>
         </is>
       </c>
-      <c r="J20" s="31" t="inlineStr">
+      <c r="J20" s="33" t="inlineStr">
         <is>
           <t>2030E</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="36" t="inlineStr">
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t>EBIT (operating income)</t>
         </is>
       </c>
-      <c r="F21" s="49">
+      <c r="F21" s="51">
         <f>IS!F26</f>
         <v/>
       </c>
-      <c r="G21" s="49">
+      <c r="G21" s="51">
         <f>IS!G26</f>
         <v/>
       </c>
-      <c r="H21" s="49">
+      <c r="H21" s="51">
         <f>IS!H26</f>
         <v/>
       </c>
-      <c r="I21" s="49">
+      <c r="I21" s="51">
         <f>IS!I26</f>
         <v/>
       </c>
-      <c r="J21" s="49">
+      <c r="J21" s="51">
         <f>IS!J26</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="38" t="inlineStr">
         <is>
           <t>Cash taxes on EBIT</t>
         </is>
@@ -10331,34 +10236,34 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="42" t="inlineStr">
+      <c r="B23" s="44" t="inlineStr">
         <is>
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="F23" s="43">
+      <c r="F23" s="45">
         <f>F21+F22</f>
         <v/>
       </c>
-      <c r="G23" s="43">
+      <c r="G23" s="45">
         <f>G21+G22</f>
         <v/>
       </c>
-      <c r="H23" s="43">
+      <c r="H23" s="45">
         <f>H21+H22</f>
         <v/>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="45">
         <f>I21+I22</f>
         <v/>
       </c>
-      <c r="J23" s="43">
+      <c r="J23" s="45">
         <f>J21+J22</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="36" t="inlineStr">
+      <c r="B24" s="38" t="inlineStr">
         <is>
           <t>Add: depreciation and amortisation</t>
         </is>
@@ -10385,7 +10290,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="36" t="inlineStr">
+      <c r="B25" s="38" t="inlineStr">
         <is>
           <t>Less: capital expenditure</t>
         </is>
@@ -10412,7 +10317,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="36" t="inlineStr">
+      <c r="B26" s="38" t="inlineStr">
         <is>
           <t>Less: stock-based compensation</t>
         </is>
@@ -10444,7 +10349,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="36" t="inlineStr">
+      <c r="B27" s="38" t="inlineStr">
         <is>
           <t>Net working capital (inventory + other assets − other liabilities)</t>
         </is>
@@ -10475,7 +10380,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="36" t="inlineStr">
+      <c r="B28" s="38" t="inlineStr">
         <is>
           <t>Less: increase in net working capital</t>
         </is>
@@ -10507,126 +10412,126 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="42" t="inlineStr">
+      <c r="B29" s="44" t="inlineStr">
         <is>
           <t>UNLEVERED FREE CASH FLOW</t>
         </is>
       </c>
-      <c r="F29" s="43">
+      <c r="F29" s="45">
         <f>F23+F24+F25+F26+F28</f>
         <v/>
       </c>
-      <c r="G29" s="43">
+      <c r="G29" s="45">
         <f>G23+G24+G25+G26+G28</f>
         <v/>
       </c>
-      <c r="H29" s="43">
+      <c r="H29" s="45">
         <f>H23+H24+H25+H26+H28</f>
         <v/>
       </c>
-      <c r="I29" s="43">
+      <c r="I29" s="45">
         <f>I23+I24+I25+I26+I28</f>
         <v/>
       </c>
-      <c r="J29" s="43">
+      <c r="J29" s="45">
         <f>J23+J24+J25+J26+J28</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="36" t="inlineStr">
+      <c r="B30" s="38" t="inlineStr">
         <is>
           <t>Period weight (2026E = Q4 only)</t>
         </is>
       </c>
-      <c r="F30" s="38" t="n">
+      <c r="F30" s="40" t="n">
         <v>0.25</v>
       </c>
-      <c r="G30" s="38" t="n">
+      <c r="G30" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="38" t="n">
+      <c r="H30" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="38" t="n">
+      <c r="I30" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="38" t="n">
+      <c r="J30" s="40" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="36" t="inlineStr">
+      <c r="B31" s="38" t="inlineStr">
         <is>
           <t>Discount period (mid-year)</t>
         </is>
       </c>
-      <c r="F31" s="38" t="n">
+      <c r="F31" s="40" t="n">
         <v>0.125</v>
       </c>
-      <c r="G31" s="38" t="n">
+      <c r="G31" s="40" t="n">
         <v>0.75</v>
       </c>
-      <c r="H31" s="38" t="n">
+      <c r="H31" s="40" t="n">
         <v>1.75</v>
       </c>
-      <c r="I31" s="38" t="n">
+      <c r="I31" s="40" t="n">
         <v>2.75</v>
       </c>
-      <c r="J31" s="38" t="n">
+      <c r="J31" s="40" t="n">
         <v>3.75</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="36" t="inlineStr">
+      <c r="B32" s="38" t="inlineStr">
         <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="F32" s="61">
+      <c r="F32" s="63">
         <f>1/(1+$C$16/100)^F31</f>
         <v/>
       </c>
-      <c r="G32" s="61">
+      <c r="G32" s="63">
         <f>1/(1+$C$16/100)^G31</f>
         <v/>
       </c>
-      <c r="H32" s="61">
+      <c r="H32" s="63">
         <f>1/(1+$C$16/100)^H31</f>
         <v/>
       </c>
-      <c r="I32" s="61">
+      <c r="I32" s="63">
         <f>1/(1+$C$16/100)^I31</f>
         <v/>
       </c>
-      <c r="J32" s="61">
+      <c r="J32" s="63">
         <f>1/(1+$C$16/100)^J31</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="42" t="inlineStr">
+      <c r="B33" s="44" t="inlineStr">
         <is>
           <t>Present value of free cash flow</t>
         </is>
       </c>
-      <c r="F33" s="43">
+      <c r="F33" s="45">
         <f>F29*F30*F32</f>
         <v/>
       </c>
-      <c r="G33" s="43">
+      <c r="G33" s="45">
         <f>G29*G30*G32</f>
         <v/>
       </c>
-      <c r="H33" s="43">
+      <c r="H33" s="45">
         <f>H29*H30*H32</f>
         <v/>
       </c>
-      <c r="I33" s="43">
+      <c r="I33" s="45">
         <f>I29*I30*I32</f>
         <v/>
       </c>
-      <c r="J33" s="43">
+      <c r="J33" s="45">
         <f>J29*J30*J32</f>
         <v/>
       </c>
@@ -10707,7 +10612,7 @@
           <t>ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="C40" s="62">
+      <c r="C40" s="64">
         <f>C36+C38</f>
         <v/>
       </c>
@@ -10734,7 +10639,7 @@
           <t>EQUITY VALUE</t>
         </is>
       </c>
-      <c r="C42" s="62">
+      <c r="C42" s="64">
         <f>C40-C41</f>
         <v/>
       </c>
@@ -10767,7 +10672,7 @@
           <t>Upside / (downside) to current price</t>
         </is>
       </c>
-      <c r="C45" s="63">
+      <c r="C45" s="65">
         <f>C44/Assumptions!$C$60-1</f>
         <v/>
       </c>
@@ -10789,153 +10694,153 @@
       <c r="J47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="22" t="inlineStr">
+      <c r="B48" s="24" t="inlineStr">
         <is>
           <t>WACC  \  terminal growth</t>
         </is>
       </c>
-      <c r="C48" s="64" t="n">
+      <c r="C48" s="66" t="n">
         <v>0.015</v>
       </c>
-      <c r="D48" s="64" t="n">
+      <c r="D48" s="66" t="n">
         <v>0.02</v>
       </c>
-      <c r="E48" s="64" t="n">
+      <c r="E48" s="66" t="n">
         <v>0.025</v>
       </c>
-      <c r="F48" s="64" t="n">
+      <c r="F48" s="66" t="n">
         <v>0.03</v>
       </c>
-      <c r="G48" s="64" t="n">
+      <c r="G48" s="66" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="65">
+      <c r="B49" s="67">
         <f>$C$16+-1.0</f>
         <v/>
       </c>
-      <c r="C49" s="66">
+      <c r="C49" s="68">
         <f>(F$29*F$30/(1+$B$49/100)^F$31+G$29*G$30/(1+$B$49/100)^G$31+H$29*H$30/(1+$B$49/100)^H$31+I$29*I$30/(1+$B$49/100)^I$31+J$29*J$30/(1+$B$49/100)^J$31+J$29*(1+C$48)/($B$49/100-C$48)/(1+$B$49/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="D49" s="66">
+      <c r="D49" s="68">
         <f>(F$29*F$30/(1+$B$49/100)^F$31+G$29*G$30/(1+$B$49/100)^G$31+H$29*H$30/(1+$B$49/100)^H$31+I$29*I$30/(1+$B$49/100)^I$31+J$29*J$30/(1+$B$49/100)^J$31+J$29*(1+D$48)/($B$49/100-D$48)/(1+$B$49/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="E49" s="66">
+      <c r="E49" s="68">
         <f>(F$29*F$30/(1+$B$49/100)^F$31+G$29*G$30/(1+$B$49/100)^G$31+H$29*H$30/(1+$B$49/100)^H$31+I$29*I$30/(1+$B$49/100)^I$31+J$29*J$30/(1+$B$49/100)^J$31+J$29*(1+E$48)/($B$49/100-E$48)/(1+$B$49/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="F49" s="66">
+      <c r="F49" s="68">
         <f>(F$29*F$30/(1+$B$49/100)^F$31+G$29*G$30/(1+$B$49/100)^G$31+H$29*H$30/(1+$B$49/100)^H$31+I$29*I$30/(1+$B$49/100)^I$31+J$29*J$30/(1+$B$49/100)^J$31+J$29*(1+F$48)/($B$49/100-F$48)/(1+$B$49/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="G49" s="66">
+      <c r="G49" s="68">
         <f>(F$29*F$30/(1+$B$49/100)^F$31+G$29*G$30/(1+$B$49/100)^G$31+H$29*H$30/(1+$B$49/100)^H$31+I$29*I$30/(1+$B$49/100)^I$31+J$29*J$30/(1+$B$49/100)^J$31+J$29*(1+G$48)/($B$49/100-G$48)/(1+$B$49/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="65">
+      <c r="B50" s="67">
         <f>$C$16+-0.5</f>
         <v/>
       </c>
-      <c r="C50" s="66">
+      <c r="C50" s="68">
         <f>(F$29*F$30/(1+$B$50/100)^F$31+G$29*G$30/(1+$B$50/100)^G$31+H$29*H$30/(1+$B$50/100)^H$31+I$29*I$30/(1+$B$50/100)^I$31+J$29*J$30/(1+$B$50/100)^J$31+J$29*(1+C$48)/($B$50/100-C$48)/(1+$B$50/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="D50" s="66">
+      <c r="D50" s="68">
         <f>(F$29*F$30/(1+$B$50/100)^F$31+G$29*G$30/(1+$B$50/100)^G$31+H$29*H$30/(1+$B$50/100)^H$31+I$29*I$30/(1+$B$50/100)^I$31+J$29*J$30/(1+$B$50/100)^J$31+J$29*(1+D$48)/($B$50/100-D$48)/(1+$B$50/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="E50" s="66">
+      <c r="E50" s="68">
         <f>(F$29*F$30/(1+$B$50/100)^F$31+G$29*G$30/(1+$B$50/100)^G$31+H$29*H$30/(1+$B$50/100)^H$31+I$29*I$30/(1+$B$50/100)^I$31+J$29*J$30/(1+$B$50/100)^J$31+J$29*(1+E$48)/($B$50/100-E$48)/(1+$B$50/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="F50" s="66">
+      <c r="F50" s="68">
         <f>(F$29*F$30/(1+$B$50/100)^F$31+G$29*G$30/(1+$B$50/100)^G$31+H$29*H$30/(1+$B$50/100)^H$31+I$29*I$30/(1+$B$50/100)^I$31+J$29*J$30/(1+$B$50/100)^J$31+J$29*(1+F$48)/($B$50/100-F$48)/(1+$B$50/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="G50" s="66">
+      <c r="G50" s="68">
         <f>(F$29*F$30/(1+$B$50/100)^F$31+G$29*G$30/(1+$B$50/100)^G$31+H$29*H$30/(1+$B$50/100)^H$31+I$29*I$30/(1+$B$50/100)^I$31+J$29*J$30/(1+$B$50/100)^J$31+J$29*(1+G$48)/($B$50/100-G$48)/(1+$B$50/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="65">
+      <c r="B51" s="67">
         <f>$C$16+0.0</f>
         <v/>
       </c>
-      <c r="C51" s="66">
+      <c r="C51" s="68">
         <f>(F$29*F$30/(1+$B$51/100)^F$31+G$29*G$30/(1+$B$51/100)^G$31+H$29*H$30/(1+$B$51/100)^H$31+I$29*I$30/(1+$B$51/100)^I$31+J$29*J$30/(1+$B$51/100)^J$31+J$29*(1+C$48)/($B$51/100-C$48)/(1+$B$51/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="D51" s="66">
+      <c r="D51" s="68">
         <f>(F$29*F$30/(1+$B$51/100)^F$31+G$29*G$30/(1+$B$51/100)^G$31+H$29*H$30/(1+$B$51/100)^H$31+I$29*I$30/(1+$B$51/100)^I$31+J$29*J$30/(1+$B$51/100)^J$31+J$29*(1+D$48)/($B$51/100-D$48)/(1+$B$51/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="E51" s="67">
+      <c r="E51" s="69">
         <f>(F$29*F$30/(1+$B$51/100)^F$31+G$29*G$30/(1+$B$51/100)^G$31+H$29*H$30/(1+$B$51/100)^H$31+I$29*I$30/(1+$B$51/100)^I$31+J$29*J$30/(1+$B$51/100)^J$31+J$29*(1+E$48)/($B$51/100-E$48)/(1+$B$51/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="F51" s="66">
+      <c r="F51" s="68">
         <f>(F$29*F$30/(1+$B$51/100)^F$31+G$29*G$30/(1+$B$51/100)^G$31+H$29*H$30/(1+$B$51/100)^H$31+I$29*I$30/(1+$B$51/100)^I$31+J$29*J$30/(1+$B$51/100)^J$31+J$29*(1+F$48)/($B$51/100-F$48)/(1+$B$51/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="G51" s="66">
+      <c r="G51" s="68">
         <f>(F$29*F$30/(1+$B$51/100)^F$31+G$29*G$30/(1+$B$51/100)^G$31+H$29*H$30/(1+$B$51/100)^H$31+I$29*I$30/(1+$B$51/100)^I$31+J$29*J$30/(1+$B$51/100)^J$31+J$29*(1+G$48)/($B$51/100-G$48)/(1+$B$51/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="65">
+      <c r="B52" s="67">
         <f>$C$16+0.5</f>
         <v/>
       </c>
-      <c r="C52" s="66">
+      <c r="C52" s="68">
         <f>(F$29*F$30/(1+$B$52/100)^F$31+G$29*G$30/(1+$B$52/100)^G$31+H$29*H$30/(1+$B$52/100)^H$31+I$29*I$30/(1+$B$52/100)^I$31+J$29*J$30/(1+$B$52/100)^J$31+J$29*(1+C$48)/($B$52/100-C$48)/(1+$B$52/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="D52" s="66">
+      <c r="D52" s="68">
         <f>(F$29*F$30/(1+$B$52/100)^F$31+G$29*G$30/(1+$B$52/100)^G$31+H$29*H$30/(1+$B$52/100)^H$31+I$29*I$30/(1+$B$52/100)^I$31+J$29*J$30/(1+$B$52/100)^J$31+J$29*(1+D$48)/($B$52/100-D$48)/(1+$B$52/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="E52" s="66">
+      <c r="E52" s="68">
         <f>(F$29*F$30/(1+$B$52/100)^F$31+G$29*G$30/(1+$B$52/100)^G$31+H$29*H$30/(1+$B$52/100)^H$31+I$29*I$30/(1+$B$52/100)^I$31+J$29*J$30/(1+$B$52/100)^J$31+J$29*(1+E$48)/($B$52/100-E$48)/(1+$B$52/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="F52" s="66">
+      <c r="F52" s="68">
         <f>(F$29*F$30/(1+$B$52/100)^F$31+G$29*G$30/(1+$B$52/100)^G$31+H$29*H$30/(1+$B$52/100)^H$31+I$29*I$30/(1+$B$52/100)^I$31+J$29*J$30/(1+$B$52/100)^J$31+J$29*(1+F$48)/($B$52/100-F$48)/(1+$B$52/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="G52" s="66">
+      <c r="G52" s="68">
         <f>(F$29*F$30/(1+$B$52/100)^F$31+G$29*G$30/(1+$B$52/100)^G$31+H$29*H$30/(1+$B$52/100)^H$31+I$29*I$30/(1+$B$52/100)^I$31+J$29*J$30/(1+$B$52/100)^J$31+J$29*(1+G$48)/($B$52/100-G$48)/(1+$B$52/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="65">
+      <c r="B53" s="67">
         <f>$C$16+1.0</f>
         <v/>
       </c>
-      <c r="C53" s="66">
+      <c r="C53" s="68">
         <f>(F$29*F$30/(1+$B$53/100)^F$31+G$29*G$30/(1+$B$53/100)^G$31+H$29*H$30/(1+$B$53/100)^H$31+I$29*I$30/(1+$B$53/100)^I$31+J$29*J$30/(1+$B$53/100)^J$31+J$29*(1+C$48)/($B$53/100-C$48)/(1+$B$53/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="D53" s="66">
+      <c r="D53" s="68">
         <f>(F$29*F$30/(1+$B$53/100)^F$31+G$29*G$30/(1+$B$53/100)^G$31+H$29*H$30/(1+$B$53/100)^H$31+I$29*I$30/(1+$B$53/100)^I$31+J$29*J$30/(1+$B$53/100)^J$31+J$29*(1+D$48)/($B$53/100-D$48)/(1+$B$53/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="E53" s="66">
+      <c r="E53" s="68">
         <f>(F$29*F$30/(1+$B$53/100)^F$31+G$29*G$30/(1+$B$53/100)^G$31+H$29*H$30/(1+$B$53/100)^H$31+I$29*I$30/(1+$B$53/100)^I$31+J$29*J$30/(1+$B$53/100)^J$31+J$29*(1+E$48)/($B$53/100-E$48)/(1+$B$53/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="F53" s="66">
+      <c r="F53" s="68">
         <f>(F$29*F$30/(1+$B$53/100)^F$31+G$29*G$30/(1+$B$53/100)^G$31+H$29*H$30/(1+$B$53/100)^H$31+I$29*I$30/(1+$B$53/100)^I$31+J$29*J$30/(1+$B$53/100)^J$31+J$29*(1+F$48)/($B$53/100-F$48)/(1+$B$53/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
-      <c r="G53" s="66">
+      <c r="G53" s="68">
         <f>(F$29*F$30/(1+$B$53/100)^F$31+G$29*G$30/(1+$B$53/100)^G$31+H$29*H$30/(1+$B$53/100)^H$31+I$29*I$30/(1+$B$53/100)^I$31+J$29*J$30/(1+$B$53/100)^J$31+J$29*(1+G$48)/($B$53/100-G$48)/(1+$B$53/100)^4.25-$C$41)/$C$43</f>
         <v/>
       </c>
